--- a/RXL_RCalc.xlsx
+++ b/RXL_RCalc.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\_RXL\Development\LAMBDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\_RXL\Development\LAMBDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E56075-AB8C-40F2-9D2D-23097E21F49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABC38DCD-8037-49C4-8BDA-E6E73B78AECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29E0D24-0EA8-4D41-8E06-9F040E158B6C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C29E0D24-0EA8-4D41-8E06-9F040E158B6C}"/>
   </bookViews>
   <sheets>
     <sheet name="RCalc" sheetId="7" r:id="rId1"/>
     <sheet name="Demo" sheetId="14" r:id="rId2"/>
-    <sheet name="Lookups" sheetId="12" r:id="rId3"/>
+    <sheet name="VBA" sheetId="15" r:id="rId3"/>
+    <sheet name="Lookups" sheetId="12" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_OnOff">Lookups!$C$6:$C$7</definedName>
     <definedName name="_YesNo">Lookups!$C$3:$C$4</definedName>
-    <definedName name="RXL_RCalc" comment="Performs a rolling calculation on a 1D input data array">_xlfn.LAMBDA(_xlpm.array,_xlpm.calculation,_xlop.ignore_blanks,_xlop.ignore_zeros,_xlop.ignore_errors,_xlop.vertical_output,_xlfn.LET(_xlpm._num,IF(ISNUMBER(_xlpm.calculation),_xlpm.calculation,IFERROR(MATCH(LOWER(_xlpm.calculation),{"sum","count","avg","min","max"},0),0)),_xlpm._igB,IF(_xlfn.ISOMITTED(_xlpm.ignore_blanks),0,_xlpm.ignore_blanks),_xlpm._igZ,IF(_xlfn.ISOMITTED(_xlpm.ignore_zeros),0,_xlpm.ignore_zeros),_xlpm._igE,IF(_xlfn.ISOMITTED(_xlpm.ignore_errors),0,_xlpm.ignore_errors),_xlpm._vOut,IF(_xlfn.ISOMITTED(_xlpm.vertical_output),-1,IF(_xlpm.vertical_output,1,0)),_xlpm._inpChk,IF(OR(AND(ROWS(_xlpm.array)&gt;1,COLUMNS(_xlpm.array)&gt;1),ROWS(_xlpm.array)&lt;1,COLUMNS(_xlpm.array)&lt;1),2,IF(OR(AND(NOT(ISLOGICAL(_xlpm._igB)),NOT(ISNUMBER(_xlpm._igB))),AND(NOT(ISLOGICAL(_xlpm._igZ)),NOT(ISNUMBER(_xlpm._igZ))),AND(NOT(ISLOGICAL(_xlpm._igE)),NOT(ISNUMBER(_xlpm._igE))),_xlpm._num&lt;1,_xlpm._num&gt;5),3,1)),_xlpm._vrt,ROWS(_xlpm.array)&gt;COLUMNS(_xlpm.array),_xlpm._fltE,IF(_xlpm._igE,IF(ISERROR(_xlpm.array)," ",_xlpm.array),_xlfn.IFNA(_xlpm.array," ")),_xlpm._fltB,IF(_xlpm._igB,IF(ISBLANK(_xlpm.array)," ",_xlpm._fltE),_xlpm._fltE),_xlpm._fltZ,IF(_xlpm._igZ,IF((--NOT(ISERROR(_xlpm.array))*--NOT(ISBLANK(_xlpm.array))*--(IFERROR(_xlpm.array," ")=0))," ",_xlpm._fltB),_xlpm._fltB),_xlpm._fst,INDEX(_xlpm._fltZ,1,1),_xlpm._init,IF((--(_xlpm._fst&lt;&gt;" ")*--NOT(ISBLANK(_xlpm._fst))*--(IFERROR(_xlpm._fst," ")=0)),_xlpm._fst,NA()),_xlpm._sum,IF(OR(_xlpm._num=1,_xlpm._num=3),_xlfn.SCAN(0,_xlpm._fltZ,_xlfn.LAMBDA(_xlpm._acc,_xlpm._val,_xlpm._acc+IF(ISNUMBER(_xlpm._val),_xlpm._val,0))),""),_xlpm._cnt,IF(OR(_xlpm._num=2,_xlpm._num=3),_xlfn.SCAN(0,_xlpm._fltZ,_xlfn.LAMBDA(_xlpm._acc,_xlpm._val,_xlpm._acc+IF(ISNUMBER(_xlpm._val),1,0))),""),_xlpm._out,CHOOSE(_xlpm._num,_xlpm._sum,_xlpm._cnt,IF(_xlpm._cnt&lt;&gt;0,_xlpm._sum/_xlpm._cnt,0),_xlfn.SCAN(_xlpm._init,_xlpm._fltZ,_xlfn.LAMBDA(_xlpm._acc,_xlpm._val,_xlfn.IFS(AND(ISNA(_xlpm._acc),ISNUMBER(_xlpm._val)),_xlpm._val,ISNUMBER(_xlpm._val),MIN(_xlpm._acc,_xlpm._val),TRUE,_xlpm._acc))),_xlfn.SCAN(_xlpm._init,_xlpm._fltZ,_xlfn.LAMBDA(_xlpm._acc,_xlpm._val,_xlfn.IFS(AND(ISNA(_xlpm._acc),ISNUMBER(_xlpm._val)),_xlpm._val,ISNUMBER(_xlpm._val),MAX(_xlpm._acc,_xlpm._val),TRUE,_xlpm._acc)))),_xlpm._rtn,_xlfn.IFS(_xlpm._vOut&lt;0,_xlpm._out,OR(AND(_xlpm._vOut, NOT(_xlpm._vrt)),AND(NOT(_xlpm._vOut),_xlpm._vrt)),TRANSPOSE(_xlpm._out),TRUE,_xlpm._out),CHOOSE(_xlpm._inpChk,_xlpm._rtn,_xlfn.LAMBDA(0),#VALUE!)))</definedName>
+    <definedName name="RXL_RCalc" comment="Performs a rolling calculation on a 1D input data array">_xlfn.LAMBDA(_xlpm.array,_xlpm.calculation,_xlop.ignore_blanks,_xlop.ignore_zeros,_xlop.ignore_errors,_xlop.vertical_output, _xlfn.LET(_xlpm._num, IF(ISNUMBER(_xlpm.calculation), _xlpm.calculation, IFERROR(MATCH(LOWER(_xlpm.calculation), {"sum","count","avg","min","max"}, 0), 0)), _xlpm._igB, IF(_xlfn.ISOMITTED(_xlpm.ignore_blanks), 0, _xlpm.ignore_blanks), _xlpm._igZ, IF(_xlfn.ISOMITTED(_xlpm.ignore_zeros), 0, _xlpm.ignore_zeros), _xlpm._igE, IF(_xlfn.ISOMITTED(_xlpm.ignore_errors), 0, _xlpm.ignore_errors), _xlpm._vOut, IF(_xlfn.ISOMITTED(_xlpm.vertical_output), -1, IF(_xlpm.vertical_output, 1, 0)), _xlpm._inpChk, IF(OR(AND(ROWS(_xlpm.array) &gt; 1, COLUMNS(_xlpm.array) &gt; 1), ROWS(_xlpm.array) &lt; 1, COLUMNS(_xlpm.array) &lt; 1), 2, IF(OR(AND(NOT(ISLOGICAL(_xlpm._igB)), NOT(ISNUMBER(_xlpm._igB))), AND(NOT(ISLOGICAL(_xlpm._igZ)), NOT(ISNUMBER(_xlpm._igZ))), AND(NOT(ISLOGICAL(_xlpm._igE)), NOT(ISNUMBER(_xlpm._igE))), _xlpm._num &lt; 1, _xlpm._num &gt; 5), 3, 1)), _xlpm._vrt, ROWS(_xlpm.array) &gt; COLUMNS(_xlpm.array), _xlpm._fltE, IF(_xlpm._igE, IF(ISERROR(_xlpm.array), " ", _xlpm.array), _xlfn.IFNA(_xlpm.array, " ")), _xlpm._fltB, IF(_xlpm._igB, IF(ISBLANK(_xlpm.array), " ", _xlpm._fltE), _xlpm._fltE), _xlpm._fltZ, IF(_xlpm._igZ, IF((--NOT(ISERROR(_xlpm.array)) * --NOT(ISBLANK(_xlpm.array)) * --(IFERROR(_xlpm.array, " ") = 0)), " ", _xlpm._fltB), _xlpm._fltB), _xlpm._fst, INDEX(_xlpm._fltZ, 1, 1), _xlpm._init, IF((--(_xlpm._fst &lt;&gt; " ") * --NOT(ISBLANK(_xlpm._fst)) * --(IFERROR(_xlpm._fst, " ") = 0)), _xlpm._fst, NA()), _xlpm._sum, IF(OR(_xlpm._num = 1, _xlpm._num = 3), _xlfn.SCAN(0, _xlpm._fltZ, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, _xlpm._acc + IF(ISNUMBER(_xlpm._val), _xlpm._val, 0))), ""), _xlpm._cnt, IF(OR(_xlpm._num = 2, _xlpm._num = 3), _xlfn.SCAN(0, _xlpm._fltZ, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, _xlpm._acc + IF(ISNUMBER(_xlpm._val), 1, 0))), ""), _xlpm._out, CHOOSE(_xlpm._num, _xlpm._sum, _xlpm._cnt, IF(_xlpm._cnt &lt;&gt; 0, _xlpm._sum / _xlpm._cnt, 0), _xlfn.SCAN(_xlpm._init, _xlpm._fltZ, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, _xlfn.IFS(AND(ISNA(_xlpm._acc), ISNUMBER(_xlpm._val)), _xlpm._val, ISNUMBER(_xlpm._val), MIN(_xlpm._acc, _xlpm._val), TRUE, _xlpm._acc))), _xlfn.SCAN(_xlpm._init, _xlpm._fltZ, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, _xlfn.IFS(AND(ISNA(_xlpm._acc), ISNUMBER(_xlpm._val)), _xlpm._val, ISNUMBER(_xlpm._val), MAX(_xlpm._acc, _xlpm._val), TRUE, _xlpm._acc)))), _xlpm._rtn, _xlfn.IFS(_xlpm._vOut &lt; 0, _xlpm._out, OR(AND(_xlpm._vOut, NOT(_xlpm._vrt)), AND(NOT(_xlpm._vOut), _xlpm._vrt)), TRANSPOSE(_xlpm._out), TRUE, _xlpm._out), CHOOSE(_xlpm._inpChk, _xlpm._rtn, _xlfn.LAMBDA(0), #VALUE!)))</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="autoNoTable"/>
   <extLst>
@@ -80,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="251">
   <si>
     <t>End of Sheet</t>
   </si>
@@ -920,6 +921,494 @@
   <si>
     <t>// Calculate the rolling SUM and COUNT values to be used for the SUM, COUNT, or AVERAGE outputs</t>
   </si>
+  <si>
+    <t xml:space="preserve">Gist URL:  </t>
+  </si>
+  <si>
+    <t>https://gist.github.com/r-silk/b124f8468b1615a40b42feda7545bc0a</t>
+  </si>
+  <si>
+    <t>Instructions</t>
+  </si>
+  <si>
+    <t>VBA Code</t>
+  </si>
+  <si>
+    <t>A.</t>
+  </si>
+  <si>
+    <t>Start by ensuring that you have this Workbook and the Workbook you wish to copy the function to open in the same Excel instance</t>
+  </si>
+  <si>
+    <t>B.</t>
+  </si>
+  <si>
+    <t>Open the VB Editor window</t>
+  </si>
+  <si>
+    <t>C.</t>
+  </si>
+  <si>
+    <t>D.</t>
+  </si>
+  <si>
+    <t>In the code window which opens for ThisWorkbook, paste the VBA code from below exactly as written</t>
+  </si>
+  <si>
+    <t>E.</t>
+  </si>
+  <si>
+    <t>After copying the VBA code into code window, update line 11 replacing the text "Example.xlsx" with the name of your Excel Workbook/file</t>
+  </si>
+  <si>
+    <t>F.</t>
+  </si>
+  <si>
+    <t>Run the CopyLambda sub routine in ThisWorkbook module and check the Immediate window for the feedback message</t>
+  </si>
+  <si>
+    <t>In order to copy across the RXL_RCalc() function from this Workbook to your own project you can use the instructions and VBA code below .</t>
+  </si>
+  <si>
+    <t>In the VB Editor Project Explorer window, select this Workbook (RXL_RCalc.xlsx) and double click on the object named "ThisWorkbook"</t>
+  </si>
+  <si>
+    <t>Also check line 7 of the code has the correct name of the function you wish to copy (i.e. "RXL_RCalc")</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Private Sub</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CopyLambda()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Dim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> wb </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>As</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Workbook, nm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>As</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Name, fn </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>As</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Name</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Dim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> strLambda </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>As String</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    'Name of custom Lambda function to copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    On Error Resume Next</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        'Update "Example.xlsx" with name of the Workbook you wish to copy the function to</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Set</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> wb = Application.Workbooks("Example.xlsx")</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">    On Error GoTo 0</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>If</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> wb </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Is Nothing Then</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Debug.Print</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> "ERROR: Destination Workbook not found - please ensure it is open"</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">        Exit Sub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    End If</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Set</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> nm = ThisWorkbook.Names(strLambda)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>If Not</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> nm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Is Nothing Then</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">        Err.Clear</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Set</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> fn = wb.Names.Add(Name:=nm.Name, _</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">                              RefersTo:=nm.RefersTo, _</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                              Visible:=nm.Visible)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>If</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Err.Number = 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Then</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">            fn.Comment = nm.Comment</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Debug.Print</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> "Success! -&gt; " &amp; strLambda &amp; " copied to " &amp; wb.Name</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">        Else</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Debug.Print</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> "ERROR: Unable to copy " &amp; strLambda &amp; " to " &amp; wb.Name</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">        End If</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Else</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E4FA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Debug.Print</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF002138"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> "ERROR: " &amp; strLambda &amp; " not found"</t>
+    </r>
+  </si>
+  <si>
+    <t>End Sub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    strLambda = "RXL_RCalc"</t>
+  </si>
 </sst>
 </file>
 
@@ -938,7 +1427,7 @@
     <numFmt numFmtId="173" formatCode="#,##0_);\(#,##0\);\ \-_)"/>
     <numFmt numFmtId="174" formatCode="0_);\(0\);\-_)"/>
   </numFmts>
-  <fonts count="49" x14ac:knownFonts="1">
+  <fonts count="52" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF002138"/>
@@ -1297,8 +1786,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF002138"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1E4FA8"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="42">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1534,6 +2043,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE4E6E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1818,7 +2333,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="94">
+  <cellStyleXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
@@ -1951,8 +2466,9 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="10" applyFill="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="11" xfId="7" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2074,11 +2590,15 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="10" xfId="93">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
+    <xf numFmtId="166" fontId="12" fillId="42" borderId="7" xfId="49" applyFill="1"/>
+    <xf numFmtId="170" fontId="12" fillId="42" borderId="7" xfId="49" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="29" fillId="42" borderId="7" xfId="77" applyFill="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="94"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="94">
+  <cellStyles count="95">
     <cellStyle name="20% - Accent1" xfId="31" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="34" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="37" builtinId="38" customBuiltin="1"/>
@@ -2122,6 +2642,7 @@
     <cellStyle name="Heading 2" xfId="8" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="9" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="10" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="94" builtinId="8"/>
     <cellStyle name="Hyperlink 2" xfId="90" xr:uid="{131D54A7-FFEA-42A6-BBDA-C3DDA18F8C7B}"/>
     <cellStyle name="Inline Check" xfId="22" xr:uid="{E7FD4D4C-BE0C-4C66-90EF-C5205204C60E}"/>
     <cellStyle name="Input" xfId="1" builtinId="20" hidden="1"/>
@@ -2151,7 +2672,7 @@
     <cellStyle name="Output - SubTotal" xfId="68" xr:uid="{3944BA35-D861-48C8-BF5E-3B5A261E1A76}"/>
     <cellStyle name="Output - Text" xfId="69" xr:uid="{D8AED5B9-3D8F-49BF-8E7D-B2C435B0B345}"/>
     <cellStyle name="Output - Total" xfId="70" xr:uid="{4535EB24-0E67-4CEB-99CB-25A662CC9E57}"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5" customBuiltin="1"/>
+    <cellStyle name="Per cent" xfId="5" builtinId="5" customBuiltin="1"/>
     <cellStyle name="Ref.In - #" xfId="77" xr:uid="{559C5B78-8ABA-490F-9260-E150F46D7C2E}"/>
     <cellStyle name="Ref.In - %" xfId="78" xr:uid="{9969ACD6-D439-497E-923B-8A61EE2BE01D}"/>
     <cellStyle name="Ref.In - Date" xfId="79" xr:uid="{45F8383B-AD4B-47DA-8A10-4D43E8A4D81C}"/>
@@ -2311,6 +2832,237 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>355542</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="A black and white logo&#10;&#10;AI-generated content may be incorrect.">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{734B7B8F-368F-47AC-81E7-F3F4CC7CA8B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30480" y="38100"/>
+          <a:ext cx="609600" cy="317442"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>511122</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>23321</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E396FDEF-237C-6422-D675-15DE9A67079B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="594360" y="3268980"/>
+          <a:ext cx="4168722" cy="3299921"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>549110</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>45842</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEF6CE29-D177-3D7D-A274-A27F091623BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="594360" y="1508760"/>
+          <a:ext cx="5425910" cy="1402202"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>435678</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>31014</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DF26D2C-D9F2-A3FD-6B7E-C1A7D59D6221}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="594361" y="7307580"/>
+          <a:ext cx="9579677" cy="3825774"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>366109</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>45797</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F37CD7D3-4247-FDCB-9A69-B4F8EE8CE344}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="594360" y="11483340"/>
+          <a:ext cx="4023709" cy="891617"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2729,59 +3481,59 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D0BDDC6-BC3B-4F1D-AEDE-0C506C7B8343}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B1:AC502"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="5" width="9.140625" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" customWidth="1"/>
+    <col min="1" max="3" width="4.33203125" customWidth="1"/>
+    <col min="4" max="5" width="9.109375" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:28" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="3:28" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C1" s="9" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C3" s="12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="4" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="6" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D6" s="42" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D7" s="42" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="8" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="9" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="11" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C11" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="12" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D12" s="14" t="s">
         <v>138</v>
       </c>
@@ -2858,7 +3610,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D13" s="14" t="s">
         <v>8</v>
       </c>
@@ -2935,7 +3687,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="14" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D14" s="14"/>
       <c r="E14" s="13">
         <v>25</v>
@@ -3006,7 +3758,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D15" s="14"/>
       <c r="E15" s="13">
         <v>25</v>
@@ -3077,7 +3829,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="2:29" s="4" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:29" s="4" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="5">
         <f xml:space="preserve"> MAX(B$1:B17) + 1</f>
         <v>1</v>
@@ -3086,7 +3838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B20" s="11" t="s">
         <v>169</v>
       </c>
@@ -3118,17 +3870,17 @@
       <c r="AB20" s="10"/>
       <c r="AC20" s="10"/>
     </row>
-    <row r="22" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C22" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D24" s="19"/>
       <c r="E24" s="16">
         <f xml:space="preserve"> D24 + E$13</f>
@@ -3227,7 +3979,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="25" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D25" s="19"/>
       <c r="E25" s="16">
         <f xml:space="preserve"> D25 + IF( OR( ISERROR(E$14), ISBLANK(E$14)), 0, E$14)</f>
@@ -3326,7 +4078,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="26" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D26" s="19"/>
       <c r="E26" s="16">
         <f xml:space="preserve"> D26 + IF( OR( ISERROR(E$15), ISBLANK(E$15)), 0, E$15)</f>
@@ -3425,18 +4177,18 @@
         <v>995</v>
       </c>
     </row>
-    <row r="28" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C28" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="E30" s="16" cm="1">
+    <row r="30" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="E30" s="58" cm="1">
         <f t="array" ref="E30:AB30" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$13:AB$13,
   _xlpm._sum, _xlfn.SCAN(0, _xlpm._arr, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, _xlpm._acc + _xlpm._val)),
@@ -3514,43 +4266,43 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="31" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E31" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E31:E35" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E30), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="32" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E32" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$13:AB$13,</v>
       </c>
     </row>
-    <row r="33" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E33" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _sum, SCAN(0, _arr, LAMBDA(_acc,_val, _acc + _val)),</v>
       </c>
     </row>
-    <row r="34" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E34" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _sum</v>
       </c>
     </row>
-    <row r="35" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="35" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E35" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="37" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="4:28" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="E38" s="16" cm="1">
+    <row r="38" spans="4:28" x14ac:dyDescent="0.3">
+      <c r="E38" s="58" cm="1">
         <f t="array" ref="E38:AB38" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$14:AB$14,
   _xlpm._sum, _xlfn.SCAN(0, _xlpm._arr, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, _xlpm._acc + IF( OR( ISERROR(_xlpm._val), ISBLANK(_xlpm._val)), 0, _xlpm._val))),
@@ -3628,43 +4380,43 @@
         <v>995</v>
       </c>
     </row>
-    <row r="39" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E39" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E39:E43" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E38), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="40" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="40" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E40" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$14:AB$14,</v>
       </c>
     </row>
-    <row r="41" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="41" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E41" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _sum, SCAN(0, _arr, LAMBDA(_acc,_val, _acc + IF( OR( ISERROR(_val), ISBLANK(_val)), 0, _val))),</v>
       </c>
     </row>
-    <row r="42" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E42" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _sum</v>
       </c>
     </row>
-    <row r="43" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="43" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E43" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="45" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="45" spans="4:28" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="E46" s="16" cm="1">
+    <row r="46" spans="4:28" x14ac:dyDescent="0.3">
+      <c r="E46" s="58" cm="1">
         <f t="array" ref="E46:AB46" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$15:AB$15,
   _xlpm._sum, _xlfn.SCAN(0, _xlpm._arr, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, _xlpm._acc + IF( OR( ISERROR(_xlpm._val), ISBLANK(_xlpm._val)), 0, _xlpm._val))),
@@ -3742,37 +4494,37 @@
         <v>995</v>
       </c>
     </row>
-    <row r="47" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E47" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E47:E51" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E46), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="48" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="48" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E48" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$15:AB$15,</v>
       </c>
     </row>
-    <row r="49" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E49" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _sum, SCAN(0, _arr, LAMBDA(_acc,_val, _acc + IF( OR( ISERROR(_val), ISBLANK(_val)), 0, _val))),</v>
       </c>
     </row>
-    <row r="50" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E50" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _sum</v>
       </c>
     </row>
-    <row r="51" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E51" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="54" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B54" s="11" t="s">
         <v>170</v>
       </c>
@@ -3804,17 +4556,17 @@
       <c r="AB54" s="10"/>
       <c r="AC54" s="10"/>
     </row>
-    <row r="56" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C56" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E58" s="16">
         <f xml:space="preserve"> COUNT($E$13:E$13)</f>
         <v>1</v>
@@ -3912,7 +4664,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D59" s="19"/>
       <c r="E59" s="16">
         <f xml:space="preserve"> D59 + IF( AND( NOT(ISERROR(E$14)), NOT(ISBLANK(E$14))), 1, 0)</f>
@@ -4011,7 +4763,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D60" s="19"/>
       <c r="E60" s="16">
         <f xml:space="preserve"> D60 + IF( AND( NOT(ISERROR(E$15)), NOT(ISBLANK(E$15)), IFERROR(E$15, 0) &lt;&gt; 0), 1, 0)</f>
@@ -4110,18 +4862,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C62" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="E64" s="16" cm="1">
+    <row r="64" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="E64" s="58" cm="1">
         <f t="array" ref="E64:AB64" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$13:AB$13,
   _xlpm._cnt, _xlfn.SCAN(0, _xlpm._arr, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, _xlpm._acc + 1)),
@@ -4199,43 +4951,43 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="65" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E65" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E65:E69" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E64), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="66" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="66" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E66" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$13:AB$13,</v>
       </c>
     </row>
-    <row r="67" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E67" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _cnt, SCAN(0, _arr, LAMBDA(_acc,_val, _acc + 1)),</v>
       </c>
     </row>
-    <row r="68" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="68" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E68" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _cnt</v>
       </c>
     </row>
-    <row r="69" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="69" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E69" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="71" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="71" spans="4:28" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="72" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="E72" s="16" cm="1">
+    <row r="72" spans="4:28" x14ac:dyDescent="0.3">
+      <c r="E72" s="58" cm="1">
         <f t="array" ref="E72:AB72" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$14:AB$14,
   _xlpm._cnt, _xlfn.SCAN(0, _xlpm._arr, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, _xlpm._acc + IF( AND( NOT(ISERROR(_xlpm._val)), NOT(ISBLANK(_xlpm._val))), 1, 0))),
@@ -4313,43 +5065,43 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E73" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E73:E77" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E72), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="74" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="74" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E74" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$14:AB$14,</v>
       </c>
     </row>
-    <row r="75" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="75" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E75" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _cnt, SCAN(0, _arr, LAMBDA(_acc,_val, _acc + IF( AND( NOT(ISERROR(_val)), NOT(ISBLANK(_val))), 1, 0))),</v>
       </c>
     </row>
-    <row r="76" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="76" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E76" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _cnt</v>
       </c>
     </row>
-    <row r="77" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E77" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="79" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="79" spans="4:28" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="E80" s="16" cm="1">
+    <row r="80" spans="4:28" x14ac:dyDescent="0.3">
+      <c r="E80" s="58" cm="1">
         <f t="array" ref="E80:AB80" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$15:AB$15,
   _xlpm._cnt, _xlfn.SCAN(0, _xlpm._arr, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, _xlpm._acc + IF( AND( NOT(ISERROR(_xlpm._val)), NOT(ISBLANK(_xlpm._val)), IFERROR(_xlpm._val, 0) &lt;&gt; 0), 1, 0))),
@@ -4427,37 +5179,37 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E81" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E81:E85" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E80), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="82" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E82" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$15:AB$15,</v>
       </c>
     </row>
-    <row r="83" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E83" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _cnt, SCAN(0, _arr, LAMBDA(_acc,_val, _acc + IF( AND( NOT(ISERROR(_val)), NOT(ISBLANK(_val)), IFERROR(_val, 0) &lt;&gt; 0), 1, 0))),</v>
       </c>
     </row>
-    <row r="84" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E84" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _cnt</v>
       </c>
     </row>
-    <row r="85" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E85" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="88" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B88" s="11" t="s">
         <v>171</v>
       </c>
@@ -4489,17 +5241,17 @@
       <c r="AB88" s="10"/>
       <c r="AC88" s="10"/>
     </row>
-    <row r="90" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C90" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="92" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E92" s="18">
         <f xml:space="preserve"> AVERAGE($E$13:E$13)</f>
         <v>25</v>
@@ -4597,7 +5349,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="93" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E93" s="18" cm="1">
         <f t="array" ref="E93" xml:space="preserve"> E25 / SUMPRODUCT(--NOT(ISERROR($E$14:E$14)) * --NOT(ISBLANK($E$14:E$14)))</f>
         <v>25</v>
@@ -4695,7 +5447,7 @@
         <v>49.75</v>
       </c>
     </row>
-    <row r="94" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E94" s="18" cm="1">
         <f t="array" ref="E94" xml:space="preserve"> _xlfn.LET(_xlpm._arr, $E$15:E$15, E26 / SUMPRODUCT(--NOT(ISERROR(_xlpm._arr)) * --NOT(ISBLANK(_xlpm._arr)) * --(IFERROR($E$15:E$15, 0) &lt;&gt; 0)))</f>
         <v>25</v>
@@ -4793,18 +5545,18 @@
         <v>55.277777777777779</v>
       </c>
     </row>
-    <row r="96" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C96" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="97" spans="4:28" x14ac:dyDescent="0.3">
       <c r="D97" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="E98" s="18" cm="1">
+    <row r="98" spans="4:28" x14ac:dyDescent="0.3">
+      <c r="E98" s="59" cm="1">
         <f t="array" ref="E98:AB98" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$13:AB$13,
   _xlpm._sum, _xlfn.SCAN(0, _xlpm._arr, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, _xlpm._acc + _xlpm._val)),
@@ -4883,49 +5635,49 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="99" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="99" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E99" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E99:E104" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E98), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="100" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="100" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E100" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$13:AB$13,</v>
       </c>
     </row>
-    <row r="101" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E101" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _sum, SCAN(0, _arr, LAMBDA(_acc,_val, _acc + _val)),</v>
       </c>
     </row>
-    <row r="102" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="102" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E102" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _cnt, SCAN(0, _arr, LAMBDA(_acc,_val, _acc + 1)),</v>
       </c>
     </row>
-    <row r="103" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="103" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E103" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  IF(_cnt &lt;&gt; 0, _sum / _cnt, 0)</v>
       </c>
     </row>
-    <row r="104" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="104" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E104" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="106" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="106" spans="4:28" x14ac:dyDescent="0.3">
       <c r="D106" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="107" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="E107" s="18" cm="1">
+    <row r="107" spans="4:28" x14ac:dyDescent="0.3">
+      <c r="E107" s="59" cm="1">
         <f t="array" ref="E107:AB107" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$14:AB$14,
   _xlpm._sum, _xlfn.SCAN(0, _xlpm._arr, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, _xlpm._acc + IF(AND(NOT(ISERROR(_xlpm._val)), NOT(ISBLANK(_xlpm._val))), _xlpm._val, 0))),
@@ -5004,49 +5756,49 @@
         <v>49.75</v>
       </c>
     </row>
-    <row r="108" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="108" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E108" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E108:E113" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E107), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="109" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="109" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E109" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$14:AB$14,</v>
       </c>
     </row>
-    <row r="110" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="110" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E110" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _sum, SCAN(0, _arr, LAMBDA(_acc,_val, _acc + IF(AND(NOT(ISERROR(_val)), NOT(ISBLANK(_val))), _val, 0))),</v>
       </c>
     </row>
-    <row r="111" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="111" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E111" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _cnt, SCAN(0, _arr, LAMBDA(_acc,_val, _acc + IF(AND(NOT(ISERROR(_val)), NOT(ISBLANK(_val))), 1, 0))),</v>
       </c>
     </row>
-    <row r="112" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="112" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E112" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  IF(_cnt &lt;&gt; 0, _sum / _cnt, 0)</v>
       </c>
     </row>
-    <row r="113" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E113" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="115" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D115" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="E116" s="18" cm="1">
+    <row r="116" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="E116" s="59" cm="1">
         <f t="array" ref="E116:AB116" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$15:AB$15,
   _xlpm._sum, _xlfn.SCAN(0, _xlpm._arr, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, _xlpm._acc + IF(AND(NOT(ISERROR(_xlpm._val)), NOT(ISBLANK(_xlpm._val)), IFERROR(_xlpm._val, 0) &lt;&gt; 0), _xlpm._val, 0))),
@@ -5125,43 +5877,43 @@
         <v>55.277777777777779</v>
       </c>
     </row>
-    <row r="117" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E117" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E117:E122" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E116), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="118" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E118" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$15:AB$15,</v>
       </c>
     </row>
-    <row r="119" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E119" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _sum, SCAN(0, _arr, LAMBDA(_acc,_val, _acc + IF(AND(NOT(ISERROR(_val)), NOT(ISBLANK(_val)), IFERROR(_val, 0) &lt;&gt; 0), _val, 0))),</v>
       </c>
     </row>
-    <row r="120" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E120" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _cnt, SCAN(0, _arr, LAMBDA(_acc,_val, _acc + IF(AND(NOT(ISERROR(_val)), NOT(ISBLANK(_val)), IFERROR(_val, 0) &lt;&gt; 0), 1, 0))),</v>
       </c>
     </row>
-    <row r="121" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E121" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  IF(_cnt &lt;&gt; 0, _sum / _cnt, 0)</v>
       </c>
     </row>
-    <row r="122" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E122" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="125" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B125" s="11" t="s">
         <v>172</v>
       </c>
@@ -5193,17 +5945,17 @@
       <c r="AB125" s="10"/>
       <c r="AC125" s="10"/>
     </row>
-    <row r="127" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C127" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D128" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="129" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="129" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D129" s="19"/>
       <c r="E129" s="16">
         <f xml:space="preserve"> IF(E$12 = 1, E$13, MIN(E$13, D129))</f>
@@ -5302,7 +6054,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="130" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="130" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D130" s="19"/>
       <c r="E130" s="16">
         <f xml:space="preserve"> IF(E$12 = 1, E$14, IF( AND( NOT(ISERROR(E$14)), NOT(ISBLANK(E$14))), MIN(E$14, D130), D130))</f>
@@ -5401,7 +6153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="131" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D131" s="19"/>
       <c r="E131" s="16">
         <f xml:space="preserve"> IF(E$12 = 1, E$15, IF( AND( NOT(ISERROR(E$15)), NOT(ISBLANK(E$15)), IFERROR(E$15, 0) &lt;&gt; 0), MIN(E$15, D131), D131))</f>
@@ -5500,18 +6252,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="133" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C133" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="134" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="134" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D134" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="135" spans="3:28" x14ac:dyDescent="0.2">
-      <c r="E135" s="16" cm="1">
+    <row r="135" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="E135" s="58" cm="1">
         <f t="array" ref="E135:AB135" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$13:AB$13,
   _xlpm._min, _xlfn.SCAN( INDEX(_xlpm._arr, 1, 1), _xlpm._arr, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, MIN(_xlpm._acc, _xlpm._val))),
@@ -5589,43 +6341,43 @@
         <v>8</v>
       </c>
     </row>
-    <row r="136" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="136" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E136" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E136:E140" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E135), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="137" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="137" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E137" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$13:AB$13,</v>
       </c>
     </row>
-    <row r="138" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="138" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E138" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _min, SCAN( INDEX(_arr, 1, 1), _arr, LAMBDA(_acc,_val, MIN(_acc, _val))),</v>
       </c>
     </row>
-    <row r="139" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="139" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E139" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _min</v>
       </c>
     </row>
-    <row r="140" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="140" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E140" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="142" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="142" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D142" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="143" spans="3:28" x14ac:dyDescent="0.2">
-      <c r="E143" s="16" cm="1">
+    <row r="143" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="E143" s="58" cm="1">
         <f t="array" ref="E143:AB143" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$14:AB$14,
   _xlpm._min, _xlfn.SCAN( INDEX(_xlpm._arr, 1, 1), _xlpm._arr, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, IF( AND( NOT(ISERROR(_xlpm._val)), NOT(ISBLANK(_xlpm._val))), MIN(_xlpm._acc, _xlpm._val), _xlpm._acc))),
@@ -5703,43 +6455,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="144" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E144" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E144:E148" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E143), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="145" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E145" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$14:AB$14,</v>
       </c>
     </row>
-    <row r="146" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E146" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _min, SCAN( INDEX(_arr, 1, 1), _arr, LAMBDA(_acc,_val, IF( AND( NOT(ISERROR(_val)), NOT(ISBLANK(_val))), MIN(_acc, _val), _acc))),</v>
       </c>
     </row>
-    <row r="147" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E147" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _min</v>
       </c>
     </row>
-    <row r="148" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E148" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="150" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D150" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="151" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="E151" s="16" cm="1">
+    <row r="151" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="E151" s="58" cm="1">
         <f t="array" ref="E151:AB151" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$15:AB$15,
   _xlpm._min, _xlfn.SCAN( INDEX(_xlpm._arr, 1, 1), _xlpm._arr, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, IF( AND( NOT(ISERROR(_xlpm._val)), NOT(ISBLANK(_xlpm._val)), IFERROR(_xlpm._val, 0) &lt;&gt; 0), MIN(_xlpm._acc, _xlpm._val), _xlpm._acc))),
@@ -5817,37 +6569,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E152" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E152:E156" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E151), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="153" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E153" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$15:AB$15,</v>
       </c>
     </row>
-    <row r="154" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E154" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _min, SCAN( INDEX(_arr, 1, 1), _arr, LAMBDA(_acc,_val, IF( AND( NOT(ISERROR(_val)), NOT(ISBLANK(_val)), IFERROR(_val, 0) &lt;&gt; 0), MIN(_acc, _val), _acc))),</v>
       </c>
     </row>
-    <row r="155" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E155" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _min</v>
       </c>
     </row>
-    <row r="156" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E156" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="159" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B159" s="11" t="s">
         <v>173</v>
       </c>
@@ -5879,17 +6631,17 @@
       <c r="AB159" s="10"/>
       <c r="AC159" s="10"/>
     </row>
-    <row r="161" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="161" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C161" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="162" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="162" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D162" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="163" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="163" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D163" s="19"/>
       <c r="E163" s="16">
         <f xml:space="preserve"> IF(E$12 = 1, E$13, MAX(E$13, D163))</f>
@@ -5988,7 +6740,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="164" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="164" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D164" s="19"/>
       <c r="E164" s="16">
         <f xml:space="preserve"> IF(E$12 = 1, E$14, IF( AND( NOT(ISERROR(E$14)), NOT(ISBLANK(E$14))), MAX(E$14, D164), D164))</f>
@@ -6087,7 +6839,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="165" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="165" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D165" s="19"/>
       <c r="E165" s="16">
         <f xml:space="preserve"> IF(E$12 = 1, E$15, IF( AND( NOT(ISERROR(E$15)), NOT(ISBLANK(E$15)), IFERROR(E$15, 0) &lt;&gt; 0), MAX(E$15, D165), D165))</f>
@@ -6186,18 +6938,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="167" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="167" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C167" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="168" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="168" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D168" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="3:28" x14ac:dyDescent="0.2">
-      <c r="E169" s="16" cm="1">
+    <row r="169" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="E169" s="58" cm="1">
         <f t="array" ref="E169:AB169" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$13:AB$13,
   _xlpm._max, _xlfn.SCAN( INDEX(_xlpm._arr, 1, 1), _xlpm._arr, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, MAX(_xlpm._acc, _xlpm._val))),
@@ -6275,43 +7027,43 @@
         <v>100</v>
       </c>
     </row>
-    <row r="170" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="170" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E170" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E170:E174" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E169), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="171" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="171" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E171" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$13:AB$13,</v>
       </c>
     </row>
-    <row r="172" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="172" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E172" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _max, SCAN( INDEX(_arr, 1, 1), _arr, LAMBDA(_acc,_val, MAX(_acc, _val))),</v>
       </c>
     </row>
-    <row r="173" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="173" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E173" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _max</v>
       </c>
     </row>
-    <row r="174" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="174" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E174" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="176" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="176" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D176" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="177" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="E177" s="16" cm="1">
+    <row r="177" spans="4:28" x14ac:dyDescent="0.3">
+      <c r="E177" s="58" cm="1">
         <f t="array" ref="E177:AB177" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$14:AB$14,
   _xlpm._max, _xlfn.SCAN( INDEX(_xlpm._arr, 1, 1), _xlpm._arr, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, IF( AND( NOT(ISERROR(_xlpm._val)), NOT(ISBLANK(_xlpm._val))), MAX(_xlpm._acc, _xlpm._val), _xlpm._acc))),
@@ -6389,43 +7141,43 @@
         <v>100</v>
       </c>
     </row>
-    <row r="178" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="178" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E178" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E178:E182" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E177), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="179" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="179" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E179" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$14:AB$14,</v>
       </c>
     </row>
-    <row r="180" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="180" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E180" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _max, SCAN( INDEX(_arr, 1, 1), _arr, LAMBDA(_acc,_val, IF( AND( NOT(ISERROR(_val)), NOT(ISBLANK(_val))), MAX(_acc, _val), _acc))),</v>
       </c>
     </row>
-    <row r="181" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="181" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E181" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _max</v>
       </c>
     </row>
-    <row r="182" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="182" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E182" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="184" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="184" spans="4:28" x14ac:dyDescent="0.3">
       <c r="D184" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="185" spans="4:28" x14ac:dyDescent="0.2">
-      <c r="E185" s="16" cm="1">
+    <row r="185" spans="4:28" x14ac:dyDescent="0.3">
+      <c r="E185" s="58" cm="1">
         <f t="array" ref="E185:AB185" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$15:AB$15,
   _xlpm._max, _xlfn.SCAN( INDEX(_xlpm._arr, 1, 1), _xlpm._arr, _xlfn.LAMBDA(_xlpm._acc,_xlpm._val, IF( AND( NOT(ISERROR(_xlpm._val)), NOT(ISBLANK(_xlpm._val)), IFERROR(_xlpm._val, 0) &lt;&gt; 0), MAX(_xlpm._acc, _xlpm._val), _xlpm._acc))),
@@ -6503,37 +7255,37 @@
         <v>100</v>
       </c>
     </row>
-    <row r="186" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="186" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E186" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E186:E190" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E185), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="187" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="187" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E187" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$15:AB$15,</v>
       </c>
     </row>
-    <row r="188" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="188" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E188" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _max, SCAN( INDEX(_arr, 1, 1), _arr, LAMBDA(_acc,_val, IF( AND( NOT(ISERROR(_val)), NOT(ISBLANK(_val)), IFERROR(_val, 0) &lt;&gt; 0), MAX(_acc, _val), _acc))),</v>
       </c>
     </row>
-    <row r="189" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="189" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E189" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _max</v>
       </c>
     </row>
-    <row r="190" spans="4:28" x14ac:dyDescent="0.2">
+    <row r="190" spans="4:28" x14ac:dyDescent="0.3">
       <c r="E190" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="193" spans="2:29" s="4" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:29" s="4" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B193" s="5">
         <f xml:space="preserve"> MAX(B$1:B192) + 1</f>
         <v>2</v>
@@ -6542,7 +7294,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="195" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B195" s="11" t="s">
         <v>20</v>
       </c>
@@ -6574,16 +7326,16 @@
       <c r="AB195" s="10"/>
       <c r="AC195" s="10"/>
     </row>
-    <row r="197" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C197" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="198" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D198" t="s">
         <v>21</v>
       </c>
-      <c r="E198" s="16" cm="1">
+      <c r="E198" s="58" cm="1">
         <f t="array" ref="E198:AB202" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E14:AB14,
   _xlpm._init, INDEX(_xlpm._arr, 1, 1),
@@ -6666,7 +7418,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="199" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D199" t="s">
         <v>22</v>
       </c>
@@ -6743,7 +7495,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="200" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D200" t="s">
         <v>23</v>
       </c>
@@ -6820,7 +7572,7 @@
         <v>49.75</v>
       </c>
     </row>
-    <row r="201" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D201" t="s">
         <v>24</v>
       </c>
@@ -6897,7 +7649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D202" t="s">
         <v>25</v>
       </c>
@@ -6974,76 +7726,76 @@
         <v>100</v>
       </c>
     </row>
-    <row r="203" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E203" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E203:E212" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E198), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="204" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E204" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E14:AB14,</v>
       </c>
     </row>
-    <row r="205" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E205" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _init, INDEX(_arr, 1, 1),</v>
       </c>
     </row>
-    <row r="206" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E206" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _sum, SCAN(0, _arr, LAMBDA(_acc,_val, _acc + IF( OR( ISERROR(_val), ISBLANK(_val)), 0, _val))),</v>
       </c>
     </row>
-    <row r="207" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E207" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _cnt, SCAN(0, _arr, LAMBDA(_acc,_val, _acc + IF( AND( NOT(ISERROR(_val)), NOT(ISBLANK(_val))), 1, 0))),</v>
       </c>
     </row>
-    <row r="208" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E208" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _min, SCAN(_init, _arr, LAMBDA(_acc,_val, IF( AND( NOT(ISERROR(_val)), NOT(ISBLANK(_val))), MIN(_acc, _val), _acc))),</v>
       </c>
     </row>
-    <row r="209" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="209" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E209" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _max, SCAN(_init, _arr, LAMBDA(_acc,_val, IF( AND( NOT(ISERROR(_val)), NOT(ISBLANK(_val))), MAX(_acc, _val), _acc))),</v>
       </c>
     </row>
-    <row r="210" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="210" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E210" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _avg, IF(_cnt &lt;&gt; 0, _sum / _cnt, 0),</v>
       </c>
     </row>
-    <row r="211" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="211" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E211" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  VSTACK(_sum, _cnt, _avg, _min, _max)</v>
       </c>
     </row>
-    <row r="212" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="212" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E212" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="214" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="214" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C214" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="215" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="215" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D215" t="s">
         <v>21</v>
       </c>
-      <c r="E215" s="16" cm="1">
+      <c r="E215" s="58" cm="1">
         <f t="array" ref="E215:AB219" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E15:AB15,
   _xlpm._init, INDEX(_xlpm._arr, 1, 1),
@@ -7126,7 +7878,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="216" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="216" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D216" t="s">
         <v>22</v>
       </c>
@@ -7203,7 +7955,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="217" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="217" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D217" t="s">
         <v>23</v>
       </c>
@@ -7280,7 +8032,7 @@
         <v>55.277777777777779</v>
       </c>
     </row>
-    <row r="218" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="218" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D218" t="s">
         <v>24</v>
       </c>
@@ -7357,7 +8109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="219" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="219" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D219" t="s">
         <v>25</v>
       </c>
@@ -7434,67 +8186,67 @@
         <v>100</v>
       </c>
     </row>
-    <row r="220" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="220" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E220" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E220:E229" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E215), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="221" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="221" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E221" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E15:AB15,</v>
       </c>
     </row>
-    <row r="222" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="222" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E222" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _init, INDEX(_arr, 1, 1),</v>
       </c>
     </row>
-    <row r="223" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="223" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E223" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _sum, SCAN(0, _arr, LAMBDA(_acc,_val, _acc + IF( OR( ISERROR(_val), ISBLANK(_val)), 0, _val))),</v>
       </c>
     </row>
-    <row r="224" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="224" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E224" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _cnt, SCAN(0, _arr, LAMBDA(_acc,_val, _acc + IF( AND( NOT(ISERROR(_val)), NOT(ISBLANK(_val)), IFERROR(_val, 0) &lt;&gt; 0), 1, 0))),</v>
       </c>
     </row>
-    <row r="225" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="225" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E225" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _min, SCAN(_init, _arr, LAMBDA(_acc,_val, IF( AND( NOT(ISERROR(_val)), NOT(ISBLANK(_val)), IFERROR(_val, 0) &lt;&gt; 0), MIN(_acc, _val), _acc))),</v>
       </c>
     </row>
-    <row r="226" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="226" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E226" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _max, SCAN(_init, _arr, LAMBDA(_acc,_val, IF( AND( NOT(ISERROR(_val)), NOT(ISBLANK(_val)), IFERROR(_val, 0) &lt;&gt; 0), MAX(_acc, _val), _acc))),</v>
       </c>
     </row>
-    <row r="227" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E227" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _avg, IF(_cnt &lt;&gt; 0, _sum / _cnt, 0),</v>
       </c>
     </row>
-    <row r="228" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="228" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E228" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  VSTACK(_sum, _cnt, _avg, _min, _max)</v>
       </c>
     </row>
-    <row r="229" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E229" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="231" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="231" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B231" s="11" t="s">
         <v>174</v>
       </c>
@@ -7526,7 +8278,7 @@
       <c r="AB231" s="10"/>
       <c r="AC231" s="10"/>
     </row>
-    <row r="233" spans="2:29" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:29" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D233" s="20" t="s">
         <v>28</v>
       </c>
@@ -7537,7 +8289,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="234" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="234" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D234" t="s">
         <v>21</v>
       </c>
@@ -7554,7 +8306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="235" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D235" t="s">
         <v>22</v>
       </c>
@@ -7583,7 +8335,7 @@
         <v>= LET(</v>
       </c>
     </row>
-    <row r="236" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="236" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D236" t="s">
         <v>23</v>
       </c>
@@ -7598,7 +8350,7 @@
         <v xml:space="preserve">  parameter, I234,</v>
       </c>
     </row>
-    <row r="237" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="237" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D237" t="s">
         <v>24</v>
       </c>
@@ -7613,7 +8365,7 @@
         <v xml:space="preserve">  _inp, IF( ISBLANK(parameter), 1, parameter),</v>
       </c>
     </row>
-    <row r="238" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="238" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D238" t="s">
         <v>25</v>
       </c>
@@ -7628,31 +8380,31 @@
         <v xml:space="preserve">  _num, IF( ISNUMBER(_inp), _inp, IFERROR( MATCH(LOWER(_inp), {"sum","count","avg","min","max"}, 0), 0)),</v>
       </c>
     </row>
-    <row r="239" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="239" spans="2:29" x14ac:dyDescent="0.3">
       <c r="J239" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _inpChk, IF( OR(_num &lt; 1, _num &gt; 5), 1, 2),</v>
       </c>
     </row>
-    <row r="240" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="240" spans="2:29" x14ac:dyDescent="0.3">
       <c r="J240" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _rtn, CHOOSE(_num, "SUM", "COUNT", "AVERAGE", "MIN", "MAX"),</v>
       </c>
     </row>
-    <row r="241" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="241" spans="2:29" x14ac:dyDescent="0.3">
       <c r="J241" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  CHOOSE(_inpChk, #VALUE!, _rtn)</v>
       </c>
     </row>
-    <row r="242" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="242" spans="2:29" x14ac:dyDescent="0.3">
       <c r="J242" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="244" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="244" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B244" s="11" t="s">
         <v>37</v>
       </c>
@@ -7684,11 +8436,11 @@
       <c r="AB244" s="10"/>
       <c r="AC244" s="10"/>
     </row>
-    <row r="246" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="246" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D246" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="E246" s="23" cm="1">
+      <c r="E246" s="60" cm="1">
         <f t="array" ref="E246:AB246" xml:space="preserve"> E12:AB12</f>
         <v>1</v>
       </c>
@@ -7762,11 +8514,11 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="247" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D247" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E247" s="23" cm="1">
+      <c r="E247" s="60" cm="1">
         <f t="array" ref="E247:AB247" xml:space="preserve"> IF( ISBLANK(E$15:AB$15), "", E$15:AB$15)</f>
         <v>25</v>
       </c>
@@ -7840,12 +8592,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="249" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="249" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C249" s="12" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="250" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="250" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D250" s="21" t="s">
         <v>45</v>
       </c>
@@ -7853,7 +8605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="251" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D251" s="21" t="s">
         <v>38</v>
       </c>
@@ -7861,7 +8613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="252" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D252" s="21" t="s">
         <v>39</v>
       </c>
@@ -7869,11 +8621,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="254" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D254" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="E254" s="16" cm="1">
+      <c r="E254" s="58" cm="1">
         <f t="array" ref="E254:AB254" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$15:AB$15,
   _xlpm._igE, IF(E250, IF( ISERROR(_xlpm._arr), "", _xlpm._arr), _xlpm._arr),
@@ -7953,7 +8705,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="255" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="255" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D255" s="21" t="s">
         <v>50</v>
       </c>
@@ -7966,48 +8718,48 @@
         <v>= LET(</v>
       </c>
     </row>
-    <row r="256" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="256" spans="2:29" x14ac:dyDescent="0.3">
       <c r="F256" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$15:AB$15,</v>
       </c>
     </row>
-    <row r="257" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="257" spans="3:28" x14ac:dyDescent="0.3">
       <c r="F257" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _igE, IF(E250, IF( ISERROR(_arr), "", _arr), _arr),</v>
       </c>
     </row>
-    <row r="258" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="258" spans="3:28" x14ac:dyDescent="0.3">
       <c r="F258" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _igB, IF(E251, IF( ISBLANK(_arr), "", _igE), _igE),</v>
       </c>
     </row>
-    <row r="259" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="259" spans="3:28" x14ac:dyDescent="0.3">
       <c r="F259" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _igZ, IF(E252, IF(_igB = 0, "", _igB), _igB),</v>
       </c>
     </row>
-    <row r="260" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="260" spans="3:28" x14ac:dyDescent="0.3">
       <c r="F260" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _igZ</v>
       </c>
     </row>
-    <row r="261" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="261" spans="3:28" x14ac:dyDescent="0.3">
       <c r="F261" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="263" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="263" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C263" s="12" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="264" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="264" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D264" s="21" t="s">
         <v>38</v>
       </c>
@@ -8015,7 +8767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="265" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D265" s="21" t="s">
         <v>39</v>
       </c>
@@ -8023,11 +8775,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="267" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D267" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E267" s="16" cm="1">
+      <c r="E267" s="58" cm="1">
         <f t="array" ref="E267:AB267" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$15:AB$15,
   _xlpm._igB, E264,
@@ -8110,7 +8862,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="268" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="268" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D268" s="21" t="s">
         <v>51</v>
       </c>
@@ -8123,61 +8875,61 @@
         <v>= LET(</v>
       </c>
     </row>
-    <row r="269" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="269" spans="3:28" x14ac:dyDescent="0.3">
       <c r="F269" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$15:AB$15,</v>
       </c>
     </row>
-    <row r="270" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="270" spans="3:28" x14ac:dyDescent="0.3">
       <c r="F270" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _igB, E264,</v>
       </c>
     </row>
-    <row r="271" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="271" spans="3:28" x14ac:dyDescent="0.3">
       <c r="F271" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _igZ, E265,</v>
       </c>
     </row>
-    <row r="272" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="272" spans="3:28" x14ac:dyDescent="0.3">
       <c r="F272" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _fltE, IF( ISERROR(_arr), " ", _arr),</v>
       </c>
     </row>
-    <row r="273" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="273" spans="2:29" x14ac:dyDescent="0.3">
       <c r="F273" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _fltB, IF(_igB, IF( ISBLANK(_arr), " ", _fltE), _fltE),</v>
       </c>
     </row>
-    <row r="274" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="274" spans="2:29" x14ac:dyDescent="0.3">
       <c r="F274" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _fltZ, IF(_igZ, IF((--NOT(ISERROR(_arr)) * --NOT(ISBLANK(_arr)) * --(IFERROR(_arr, " ") = 0)), " ", _fltB), _fltB),</v>
       </c>
     </row>
-    <row r="275" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="275" spans="2:29" x14ac:dyDescent="0.3">
       <c r="F275" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _cnt, SCAN(0, _fltZ, LAMBDA(_acc,_val, _acc + IF( ISNUMBER(_val), 1, 0))),</v>
       </c>
     </row>
-    <row r="276" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="276" spans="2:29" x14ac:dyDescent="0.3">
       <c r="F276" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _cnt</v>
       </c>
     </row>
-    <row r="277" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="277" spans="2:29" x14ac:dyDescent="0.3">
       <c r="F277" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="279" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="279" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B279" s="11" t="s">
         <v>47</v>
       </c>
@@ -8209,18 +8961,18 @@
       <c r="AB279" s="10"/>
       <c r="AC279" s="10"/>
     </row>
-    <row r="281" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="281" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C281" s="12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="283" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="283" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D283" s="21" t="s">
         <v>46</v>
       </c>
       <c r="E283" s="27"/>
     </row>
-    <row r="284" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="284" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D284" s="21" t="s">
         <v>38</v>
       </c>
@@ -8228,7 +8980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="285" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D285" s="21" t="s">
         <v>39</v>
       </c>
@@ -8236,8 +8988,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="E287" s="16" cm="1">
+    <row r="287" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="E287" s="58" cm="1">
         <f t="array" ref="E287:AB287" xml:space="preserve"> _xlfn.LET(
   _xlpm._arr, E$15:AB$15,
   _xlpm._calc, IF( ISBLANK(E283), 1, E283),
@@ -8343,213 +9095,213 @@
         <v>995</v>
       </c>
     </row>
-    <row r="288" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="288" spans="2:29" x14ac:dyDescent="0.3">
       <c r="E288" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="E288:E320" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E287), , CHAR(10))</f>
         <v>= LET(</v>
       </c>
     </row>
-    <row r="289" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="289" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E289" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _arr, E$15:AB$15,</v>
       </c>
     </row>
-    <row r="290" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="290" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E290" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _calc, IF( ISBLANK(E283), 1, E283),</v>
       </c>
     </row>
-    <row r="291" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="291" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E291" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _num, IF( ISNUMBER(_calc), _calc, IFERROR( MATCH(LOWER(_calc), {"sum","count","avg","min","max"}, 0), 0)),</v>
       </c>
     </row>
-    <row r="292" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="292" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E292" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _igB, IF( ISBLANK(E284), 0, E284),</v>
       </c>
     </row>
-    <row r="293" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="293" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E293" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _igZ, IF( ISBLANK(E285), 0, E285),</v>
       </c>
     </row>
-    <row r="294" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="294" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E294" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _inpChk, IF( OR(</v>
       </c>
     </row>
-    <row r="295" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="295" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E295" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    AND( ROWS(_arr) &gt; 1, COLUMNS(_arr) &gt; 1),</v>
       </c>
     </row>
-    <row r="296" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="296" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E296" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    ROWS(_arr) &lt; 1, COLUMNS(_arr) &lt; 1,</v>
       </c>
     </row>
-    <row r="297" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="297" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E297" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _num &lt; 1, _num &gt; 5</v>
       </c>
     </row>
-    <row r="298" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="298" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E298" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  ), 2, 1),</v>
       </c>
     </row>
-    <row r="299" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="299" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E299" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _fltE, IF( ISERROR(_arr), " ", _arr),</v>
       </c>
     </row>
-    <row r="300" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="300" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E300" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _fltB, IF(_igB, IF( ISBLANK(_arr), " ", _fltE), _fltE),</v>
       </c>
     </row>
-    <row r="301" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="301" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E301" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _fltZ, IF(_igZ, IF((--NOT(ISERROR(_arr)) * --NOT(ISBLANK(_arr)) * --(IFERROR(_arr, " ") = 0)), " ", _fltB), _fltB),</v>
       </c>
     </row>
-    <row r="302" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="302" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E302" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _fst, INDEX(_fltZ, 1, 1),</v>
       </c>
     </row>
-    <row r="303" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="303" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E303" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _init, IF((--(_fst &lt;&gt; " ") * --NOT(ISBLANK(_fst)) * --(IFERROR(_fst, " ") = 0)), _fst, NA()),</v>
       </c>
     </row>
-    <row r="304" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="304" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E304" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _sum, IF( OR(_num = 1, _num = 3),</v>
       </c>
     </row>
-    <row r="305" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="305" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E305" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    SCAN(0, _fltZ, LAMBDA(_acc,_val, _acc + IF( ISNUMBER(_val), _val, 0))),</v>
       </c>
     </row>
-    <row r="306" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="306" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E306" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    ""</v>
       </c>
     </row>
-    <row r="307" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="307" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E307" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  ),</v>
       </c>
     </row>
-    <row r="308" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="308" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E308" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _cnt, IF( OR(_num = 2, _num = 3),</v>
       </c>
     </row>
-    <row r="309" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="309" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E309" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    SCAN(0, _fltZ, LAMBDA(_acc,_val, _acc + IF( ISNUMBER(_val), 1, 0))),</v>
       </c>
     </row>
-    <row r="310" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="310" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E310" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    ""</v>
       </c>
     </row>
-    <row r="311" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="311" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E311" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  ),</v>
       </c>
     </row>
-    <row r="312" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="312" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E312" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  _out, CHOOSE(_num,</v>
       </c>
     </row>
-    <row r="313" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="313" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E313" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _sum,</v>
       </c>
     </row>
-    <row r="314" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="314" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E314" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _cnt,</v>
       </c>
     </row>
-    <row r="315" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="315" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E315" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    IF(_cnt &lt;&gt; 0, _sum / _cnt, 0),</v>
       </c>
     </row>
-    <row r="316" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="316" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E316" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    SCAN(_init, _fltZ, LAMBDA(_acc,_val, IFS( AND( ISNA(_acc), ISNUMBER(_val)), _val, ISNUMBER(_val), MIN(_acc, _val), TRUE, _acc))),</v>
       </c>
     </row>
-    <row r="317" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="317" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E317" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    SCAN(_init, _fltZ, LAMBDA(_acc,_val, IFS( AND( ISNA(_acc), ISNUMBER(_val)), _val, ISNUMBER(_val), MAX(_acc, _val), TRUE, _acc)))</v>
       </c>
     </row>
-    <row r="318" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="318" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E318" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  ),</v>
       </c>
     </row>
-    <row r="319" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="319" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E319" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  CHOOSE(_inpChk, _out, #VALUE!)</v>
       </c>
     </row>
-    <row r="320" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="320" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E320" s="17" t="str">
         <f ca="1"/>
         <v>)</v>
       </c>
     </row>
-    <row r="321" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="321" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E321" s="17"/>
     </row>
-    <row r="322" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="322" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C322" s="12" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="324" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="324" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D324" s="21" t="s">
         <v>46</v>
       </c>
@@ -8557,7 +9309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="325" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D325" s="21" t="s">
         <v>38</v>
       </c>
@@ -8565,7 +9317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="326" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D326" s="21" t="s">
         <v>39</v>
       </c>
@@ -8573,7 +9325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="327" spans="3:28" x14ac:dyDescent="0.3">
       <c r="D327" s="21" t="s">
         <v>49</v>
       </c>
@@ -8581,8 +9333,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="3:28" x14ac:dyDescent="0.2">
-      <c r="E329" s="16" cm="1">
+    <row r="329" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="E329" s="58" cm="1">
         <f t="array" ref="E329:AB329" xml:space="preserve"> _xlfn.LAMBDA(_xlpm.array,_xlpm.calculation,_xlop.ignore_blanks,_xlop.ignore_zeros,_xlop.vertical_output,
   _xlfn.LET(
     _xlpm._num, IF( ISNUMBER(_xlpm.calculation), _xlpm.calculation, IFERROR( MATCH(LOWER(_xlpm.calculation), {"sum","count","avg","min","max"}, 0), 0)),
@@ -8705,330 +9457,330 @@
         <v>995</v>
       </c>
     </row>
-    <row r="330" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="330" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E330" s="16"/>
       <c r="F330" s="17" t="str" cm="1">
         <f t="array" aca="1" ref="F330:F379" ca="1" xml:space="preserve"> _xlfn.TEXTSPLIT( _xlfn.FORMULATEXT(E329), , CHAR(10))</f>
         <v>= LAMBDA(array,calculation,[ignore_blanks],[ignore_zeros],[vertical_output],</v>
       </c>
     </row>
-    <row r="331" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="331" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E331" s="16"/>
       <c r="F331" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  LET(</v>
       </c>
     </row>
-    <row r="332" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="332" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E332" s="16"/>
       <c r="F332" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _num, IF( ISNUMBER(calculation), calculation, IFERROR( MATCH(LOWER(calculation), {"sum","count","avg","min","max"}, 0), 0)),</v>
       </c>
     </row>
-    <row r="333" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="333" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E333" s="16"/>
       <c r="F333" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _igB, IF( ISOMITTED(ignore_blanks), 0, ignore_blanks),</v>
       </c>
     </row>
-    <row r="334" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="334" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E334" s="16"/>
       <c r="F334" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _igZ, IF( ISOMITTED(ignore_zeros), 0, ignore_zeros),</v>
       </c>
     </row>
-    <row r="335" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="335" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E335" s="16"/>
       <c r="F335" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _vOut, IF( ISOMITTED(vertical_output), -1, IF(vertical_output, 1, 0)),</v>
       </c>
     </row>
-    <row r="336" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="336" spans="3:28" x14ac:dyDescent="0.3">
       <c r="E336" s="16"/>
       <c r="F336" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _inpChk, IF( OR(</v>
       </c>
     </row>
-    <row r="337" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="337" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E337" s="16"/>
       <c r="F337" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      AND( ROWS(array) &gt; 1, COLUMNS(array) &gt; 1),</v>
       </c>
     </row>
-    <row r="338" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="338" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E338" s="16"/>
       <c r="F338" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      ROWS(array) &lt; 1, COLUMNS(array) &lt; 1),</v>
       </c>
     </row>
-    <row r="339" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="339" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E339" s="16"/>
       <c r="F339" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      2,</v>
       </c>
     </row>
-    <row r="340" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="340" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E340" s="16"/>
       <c r="F340" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      IF( OR(</v>
       </c>
     </row>
-    <row r="341" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="341" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E341" s="16"/>
       <c r="F341" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">        AND( NOT(ISLOGICAL(_igB)), NOT(ISNUMBER(_igB))),</v>
       </c>
     </row>
-    <row r="342" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="342" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E342" s="16"/>
       <c r="F342" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">        AND( NOT(ISLOGICAL(_igZ)), NOT(ISNUMBER(_igZ))),</v>
       </c>
     </row>
-    <row r="343" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="343" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E343" s="16"/>
       <c r="F343" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">        _num &lt; 1, _num &gt; 5),</v>
       </c>
     </row>
-    <row r="344" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="344" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E344" s="16"/>
       <c r="F344" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">        3, 1</v>
       </c>
     </row>
-    <row r="345" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="345" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E345" s="16"/>
       <c r="F345" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      )</v>
       </c>
     </row>
-    <row r="346" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="346" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E346" s="16"/>
       <c r="F346" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    ),</v>
       </c>
     </row>
-    <row r="347" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="347" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E347" s="16"/>
       <c r="F347" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _vrt, ROWS(array) &gt; COLUMNS(array),</v>
       </c>
     </row>
-    <row r="348" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="348" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E348" s="16"/>
       <c r="F348" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _fltE, IF( ISERROR(array), " ", array),</v>
       </c>
     </row>
-    <row r="349" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="349" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E349" s="16"/>
       <c r="F349" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _fltB, IF(_igB, IF( ISBLANK(array), " ", _fltE), _fltE),</v>
       </c>
     </row>
-    <row r="350" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="350" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E350" s="16"/>
       <c r="F350" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _fltZ, IF(_igZ, IF((--NOT(ISERROR(array)) * --NOT(ISBLANK(array)) * --(IFERROR(array, " ") = 0)), " ", _fltB), _fltB),</v>
       </c>
     </row>
-    <row r="351" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="351" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E351" s="16"/>
       <c r="F351" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _fst, INDEX(_fltZ, 1, 1),</v>
       </c>
     </row>
-    <row r="352" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="352" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E352" s="16"/>
       <c r="F352" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _init, IF((--(_fst &lt;&gt; " ") * --NOT(ISBLANK(_fst)) * --(IFERROR(_fst, " ") = 0)), _fst, NA()),</v>
       </c>
     </row>
-    <row r="353" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="353" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F353" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _sum, IF( OR(_num = 1, _num = 3),</v>
       </c>
     </row>
-    <row r="354" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="354" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F354" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      SCAN(0, _fltZ, LAMBDA(_acc,_val, _acc + IF( ISNUMBER(_val), _val, 0))),</v>
       </c>
     </row>
-    <row r="355" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="355" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F355" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      ""</v>
       </c>
     </row>
-    <row r="356" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="356" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F356" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    ),</v>
       </c>
     </row>
-    <row r="357" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="357" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F357" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _cnt, IF( OR(_num = 2, _num = 3),</v>
       </c>
     </row>
-    <row r="358" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="358" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F358" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      SCAN(0, _fltZ, LAMBDA(_acc,_val, _acc + IF( ISNUMBER(_val), 1, 0))),</v>
       </c>
     </row>
-    <row r="359" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="359" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F359" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      ""</v>
       </c>
     </row>
-    <row r="360" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="360" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F360" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    ),</v>
       </c>
     </row>
-    <row r="361" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="361" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F361" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _out, CHOOSE(_num,</v>
       </c>
     </row>
-    <row r="362" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="362" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F362" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      _sum,</v>
       </c>
     </row>
-    <row r="363" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="363" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F363" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      _cnt,</v>
       </c>
     </row>
-    <row r="364" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="364" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F364" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      IF(_cnt &lt;&gt; 0, _sum / _cnt, 0),</v>
       </c>
     </row>
-    <row r="365" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="365" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F365" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      SCAN(_init, _fltZ, LAMBDA(_acc,_val, IFS( AND( ISNA(_acc), ISNUMBER(_val)), _val, ISNUMBER(_val), MIN(_acc, _val), TRUE, _acc))),</v>
       </c>
     </row>
-    <row r="366" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="366" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F366" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      SCAN(_init, _fltZ, LAMBDA(_acc,_val, IFS( AND( ISNA(_acc), ISNUMBER(_val)), _val, ISNUMBER(_val), MAX(_acc, _val), TRUE, _acc)))</v>
       </c>
     </row>
-    <row r="367" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="367" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F367" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    ),</v>
       </c>
     </row>
-    <row r="368" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="368" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F368" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    _rtn, IFS(</v>
       </c>
     </row>
-    <row r="369" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="369" spans="2:6" x14ac:dyDescent="0.3">
       <c r="F369" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      _vOut &lt; 0, _out,</v>
       </c>
     </row>
-    <row r="370" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="370" spans="2:6" x14ac:dyDescent="0.3">
       <c r="F370" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      OR(</v>
       </c>
     </row>
-    <row r="371" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="371" spans="2:6" x14ac:dyDescent="0.3">
       <c r="F371" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">        AND(_vOut, NOT(_vrt)),</v>
       </c>
     </row>
-    <row r="372" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="372" spans="2:6" x14ac:dyDescent="0.3">
       <c r="F372" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">        AND(NOT(_vOut), _vrt)</v>
       </c>
     </row>
-    <row r="373" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="373" spans="2:6" x14ac:dyDescent="0.3">
       <c r="F373" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      ),</v>
       </c>
     </row>
-    <row r="374" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="374" spans="2:6" x14ac:dyDescent="0.3">
       <c r="F374" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      TRANSPOSE(_out),</v>
       </c>
     </row>
-    <row r="375" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="375" spans="2:6" x14ac:dyDescent="0.3">
       <c r="F375" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">      TRUE, _out</v>
       </c>
     </row>
-    <row r="376" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="376" spans="2:6" x14ac:dyDescent="0.3">
       <c r="F376" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    ),</v>
       </c>
     </row>
-    <row r="377" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="377" spans="2:6" x14ac:dyDescent="0.3">
       <c r="F377" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    CHOOSE(_inpChk, _rtn, LAMBDA(0), #VALUE!)</v>
       </c>
     </row>
-    <row r="378" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="378" spans="2:6" x14ac:dyDescent="0.3">
       <c r="F378" s="17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">  )</v>
       </c>
     </row>
-    <row r="379" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="379" spans="2:6" x14ac:dyDescent="0.3">
       <c r="F379" s="17" t="str">
         <f ca="1"/>
         <v>)(E$15:AB$15, E324, E325, E326, E327)</v>
       </c>
     </row>
-    <row r="382" spans="2:6" s="4" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="2:6" s="4" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B382" s="5">
         <f xml:space="preserve"> MAX(B$1:B381) + 1</f>
         <v>3</v>
@@ -9037,47 +9789,47 @@
         <v>7</v>
       </c>
     </row>
-    <row r="384" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="384" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C384" s="28" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="385" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="385" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D385" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="386" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="386" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D386" s="42" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="387" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="387" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D387" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="388" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="388" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D388" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="389" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="389" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D389" s="42" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="390" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="390" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D390" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="392" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="392" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C392" s="28" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="393" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="393" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D393" s="29" t="s">
         <v>57</v>
       </c>
@@ -9088,7 +9840,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="394" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="394" spans="3:11" x14ac:dyDescent="0.3">
       <c r="G394" s="41" t="s">
         <v>117</v>
       </c>
@@ -9096,12 +9848,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="395" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="395" spans="3:11" x14ac:dyDescent="0.3">
       <c r="K395" s="41" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="396" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="396" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D396" s="29" t="s">
         <v>58</v>
       </c>
@@ -9112,12 +9864,12 @@
         <v>182</v>
       </c>
     </row>
-    <row r="397" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="397" spans="3:11" x14ac:dyDescent="0.3">
       <c r="G397" s="42" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="398" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="398" spans="3:11" x14ac:dyDescent="0.3">
       <c r="G398" s="45">
         <v>1</v>
       </c>
@@ -9128,7 +9880,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="399" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="399" spans="3:11" x14ac:dyDescent="0.3">
       <c r="G399" s="45">
         <v>2</v>
       </c>
@@ -9139,7 +9891,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="400" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="400" spans="3:11" x14ac:dyDescent="0.3">
       <c r="G400" s="45">
         <v>3</v>
       </c>
@@ -9150,7 +9902,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="401" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="401" spans="4:9" x14ac:dyDescent="0.3">
       <c r="G401" s="45">
         <v>4</v>
       </c>
@@ -9161,7 +9913,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="402" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="402" spans="4:9" x14ac:dyDescent="0.3">
       <c r="G402" s="45">
         <v>5</v>
       </c>
@@ -9172,7 +9924,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="403" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="403" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D403" s="43" t="s">
         <v>59</v>
       </c>
@@ -9183,17 +9935,17 @@
         <v>183</v>
       </c>
     </row>
-    <row r="404" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="404" spans="4:9" x14ac:dyDescent="0.3">
       <c r="G404" s="42" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="405" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="405" spans="4:9" x14ac:dyDescent="0.3">
       <c r="G405" s="42" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="406" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="406" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D406" s="29" t="s">
         <v>60</v>
       </c>
@@ -9204,17 +9956,17 @@
         <v>184</v>
       </c>
     </row>
-    <row r="407" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="407" spans="4:9" x14ac:dyDescent="0.3">
       <c r="G407" s="42" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="408" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="408" spans="4:9" x14ac:dyDescent="0.3">
       <c r="G408" s="42" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="409" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="409" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D409" s="29" t="s">
         <v>197</v>
       </c>
@@ -9225,24 +9977,24 @@
         <v>198</v>
       </c>
     </row>
-    <row r="410" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="410" spans="4:9" x14ac:dyDescent="0.3">
       <c r="G410" s="42" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="411" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="411" spans="4:9" x14ac:dyDescent="0.3">
       <c r="G411" s="42" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="412" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="412" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D412" s="29"/>
       <c r="F412" s="40"/>
-      <c r="G412" s="58" t="s">
+      <c r="G412" s="42" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="413" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="413" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D413" s="29" t="s">
         <v>61</v>
       </c>
@@ -9253,22 +10005,22 @@
         <v>118</v>
       </c>
     </row>
-    <row r="414" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="414" spans="4:9" x14ac:dyDescent="0.3">
       <c r="G414" s="42" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="415" spans="4:9" x14ac:dyDescent="0.2">
+    <row r="415" spans="4:9" x14ac:dyDescent="0.3">
       <c r="G415" s="42" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="417" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="417" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C417" s="28" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="418" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="418" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D418" s="30" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -9276,7 +10028,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="419" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="419" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D419" s="30" t="e">
         <v>#VALUE!</v>
       </c>
@@ -9284,7 +10036,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="420" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="420" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D420" s="30" t="e">
         <v>#VALUE!</v>
       </c>
@@ -9292,393 +10044,393 @@
         <v>200</v>
       </c>
     </row>
-    <row r="422" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="422" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C422" s="28" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="423" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="423" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D423" s="31" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="424" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="424" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D424" s="37" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="425" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="425" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D425" s="36" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="426" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="426" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D426" s="36" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="427" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="427" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D427" s="36" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="428" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="428" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D428" s="36" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="429" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="429" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D429" s="36" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="430" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="430" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D430" s="36" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="431" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="431" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D431" s="37" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="432" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="432" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D432" s="32" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="433" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="433" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D433" s="38" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="434" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="434" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D434" s="33" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="435" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="435" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D435" s="38" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="436" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="436" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D436" s="33" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="437" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="437" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D437" s="33" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="438" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="438" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D438" s="33" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="439" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="439" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D439" s="33" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="440" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="440" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D440" s="38" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="441" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="441" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D441" s="38" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="442" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="442" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D442" s="38" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="443" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="443" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D443" s="33" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="444" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="444" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D444" s="34" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="445" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="445" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D445" s="34" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="446" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="446" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D446" s="34" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="447" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="447" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D447" s="34" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="448" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="448" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D448" s="35" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="449" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="449" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D449" s="35" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="450" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="450" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D450" s="35" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="451" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="451" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D451" s="35" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="452" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="452" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D452" s="35" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="453" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="453" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D453" s="34" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="454" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="454" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D454" s="33" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="455" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="455" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D455" s="38" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="456" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="456" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D456" s="33" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="457" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="457" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D457" s="38" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="458" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="458" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D458" s="33" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="459" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="459" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D459" s="33" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="460" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="460" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D460" s="33" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="461" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="461" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D461" s="38" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="462" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="462" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D462" s="38" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="463" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="463" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D463" s="38" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="464" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="464" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D464" s="33" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="465" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="465" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D465" s="33" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="466" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="466" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D466" s="38" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="467" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="467" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D467" s="33" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="468" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="468" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D468" s="34" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="469" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="469" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D469" s="34" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="470" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="470" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D470" s="33" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="471" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="471" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D471" s="33" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="472" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="472" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D472" s="34" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="473" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="473" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D473" s="34" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="474" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="474" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D474" s="33" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="475" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="475" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D475" s="38" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="476" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="476" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D476" s="33" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="477" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="477" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D477" s="34" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="478" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="478" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D478" s="34" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="479" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="479" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D479" s="34" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="480" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="480" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D480" s="34" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="481" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="481" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D481" s="34" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="482" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="482" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D482" s="33" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="483" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="483" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D483" s="38" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="484" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="484" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D484" s="33" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="485" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="485" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D485" s="34" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="486" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="486" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D486" s="34" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="487" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="487" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D487" s="35" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="488" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="488" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D488" s="35" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="489" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="489" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D489" s="34" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="490" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="490" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D490" s="34" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="491" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="491" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D491" s="34" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="492" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="492" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D492" s="33" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="493" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="493" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D493" s="38" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="494" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="494" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D494" s="33" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="495" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="495" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D495" s="32" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="496" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="496" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D496" s="29" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="498" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="498" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C498" s="28" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="499" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="499" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D499" s="31" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="501" spans="2:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="502" spans="2:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="2:4" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="502" spans="2:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B502" s="2" t="s">
         <v>0</v>
       </c>
@@ -9697,20 +10449,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADCFE05A-0CD4-4205-96D0-265E6C54E31B}">
-  <dimension ref="A1:S87"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:S89"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="4.28515625" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="1" max="2" width="4.33203125" customWidth="1"/>
+    <col min="3" max="3" width="4.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="48" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="48" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="49"/>
       <c r="C1" s="9" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="4" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" s="4" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="5">
         <f xml:space="preserve"> MAX(B1:B1) + 1</f>
         <v>1</v>
@@ -9719,7 +10472,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D4" s="50" t="s">
         <v>147</v>
       </c>
@@ -9728,7 +10481,7 @@
       </c>
       <c r="Q4" s="44"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D5" s="50" t="s">
         <v>149</v>
       </c>
@@ -9736,124 +10489,44 @@
         <v>186</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B7" s="11" t="s">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D6" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="E6" s="61" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B9" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C11" s="12" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D10" s="51" t="s">
+    <row r="12" spans="1:19" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D12" s="51" t="s">
         <v>152</v>
-      </c>
-      <c r="E10" s="52">
-        <v>6</v>
-      </c>
-      <c r="F10" s="53">
-        <v>9</v>
-      </c>
-      <c r="G10" s="53">
-        <v>11</v>
-      </c>
-      <c r="H10" s="53">
-        <v>2</v>
-      </c>
-      <c r="I10" s="53">
-        <v>14</v>
-      </c>
-      <c r="J10" s="53">
-        <v>3</v>
-      </c>
-      <c r="K10" s="53">
-        <v>7</v>
-      </c>
-      <c r="L10" s="53">
-        <v>11</v>
-      </c>
-      <c r="M10" s="53">
-        <v>10</v>
-      </c>
-      <c r="N10" s="53">
-        <v>19</v>
-      </c>
-      <c r="O10" s="53">
-        <v>2</v>
-      </c>
-      <c r="P10" s="53">
-        <v>16</v>
-      </c>
-      <c r="R10" s="54" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="D11" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="E11" s="52">
-        <v>6</v>
-      </c>
-      <c r="F11" s="53">
-        <v>9</v>
-      </c>
-      <c r="G11" s="53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H11" s="53">
-        <v>2</v>
-      </c>
-      <c r="I11" s="53">
-        <v>14</v>
-      </c>
-      <c r="J11" s="53">
-        <v>3</v>
-      </c>
-      <c r="K11" s="53">
-        <v>7</v>
-      </c>
-      <c r="L11" s="53">
-        <v>11</v>
-      </c>
-      <c r="M11" s="53">
-        <v>10</v>
-      </c>
-      <c r="N11" s="53">
-        <v>19</v>
-      </c>
-      <c r="O11" s="53">
-        <v>2</v>
-      </c>
-      <c r="P11" s="53">
-        <v>16</v>
-      </c>
-      <c r="R11" s="55">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="D12" s="51" t="s">
-        <v>155</v>
       </c>
       <c r="E12" s="52">
         <v>6</v>
@@ -9861,8 +10534,8 @@
       <c r="F12" s="53">
         <v>9</v>
       </c>
-      <c r="G12" s="53" t="e">
-        <v>#N/A</v>
+      <c r="G12" s="53">
+        <v>11</v>
       </c>
       <c r="H12" s="53">
         <v>2</v>
@@ -9877,7 +10550,7 @@
         <v>7</v>
       </c>
       <c r="L12" s="53">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M12" s="53">
         <v>10</v>
@@ -9891,13 +10564,13 @@
       <c r="P12" s="53">
         <v>16</v>
       </c>
-      <c r="R12" s="53">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="R12" s="54" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D13" s="51" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E13" s="52">
         <v>6</v>
@@ -9908,16 +10581,20 @@
       <c r="G13" s="53" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H13" s="53"/>
+      <c r="H13" s="53">
+        <v>2</v>
+      </c>
       <c r="I13" s="53">
         <v>14</v>
       </c>
-      <c r="J13" s="53"/>
+      <c r="J13" s="53">
+        <v>3</v>
+      </c>
       <c r="K13" s="53">
         <v>7</v>
       </c>
       <c r="L13" s="53">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M13" s="53">
         <v>10</v>
@@ -9931,38 +10608,77 @@
       <c r="P13" s="53">
         <v>16</v>
       </c>
-      <c r="R13" s="53">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="R13" s="55">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D14" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" s="52">
+        <v>6</v>
+      </c>
+      <c r="F14" s="53">
+        <v>9</v>
+      </c>
+      <c r="G14" s="53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H14" s="53">
+        <v>2</v>
+      </c>
+      <c r="I14" s="53">
+        <v>14</v>
+      </c>
+      <c r="J14" s="53">
+        <v>3</v>
+      </c>
+      <c r="K14" s="53">
+        <v>7</v>
+      </c>
+      <c r="L14" s="53">
+        <v>0</v>
+      </c>
+      <c r="M14" s="53">
+        <v>10</v>
+      </c>
+      <c r="N14" s="53">
+        <v>19</v>
+      </c>
+      <c r="O14" s="53">
+        <v>2</v>
+      </c>
+      <c r="P14" s="53">
+        <v>16</v>
+      </c>
       <c r="R14" s="53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D15" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="E15" s="52"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53">
-        <v>0</v>
-      </c>
-      <c r="H15" s="53">
-        <v>2</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="E15" s="52">
+        <v>6</v>
+      </c>
+      <c r="F15" s="53">
+        <v>9</v>
+      </c>
+      <c r="G15" s="53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H15" s="53"/>
       <c r="I15" s="53">
         <v>14</v>
       </c>
-      <c r="J15" s="53">
-        <v>3</v>
-      </c>
+      <c r="J15" s="53"/>
       <c r="K15" s="53">
         <v>7</v>
       </c>
       <c r="L15" s="53">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M15" s="53">
         <v>10</v>
@@ -9977,1091 +10693,1414 @@
         <v>16</v>
       </c>
       <c r="R15" s="53">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R16" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="D17" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" s="52"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53">
+        <v>0</v>
+      </c>
+      <c r="H17" s="53">
+        <v>2</v>
+      </c>
+      <c r="I17" s="53">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="D16" s="51" t="s">
+      <c r="J17" s="53">
+        <v>3</v>
+      </c>
+      <c r="K17" s="53">
+        <v>7</v>
+      </c>
+      <c r="L17" s="53">
+        <v>11</v>
+      </c>
+      <c r="M17" s="53">
+        <v>10</v>
+      </c>
+      <c r="N17" s="53">
+        <v>19</v>
+      </c>
+      <c r="O17" s="53">
+        <v>2</v>
+      </c>
+      <c r="P17" s="53">
+        <v>16</v>
+      </c>
+      <c r="R17" s="53">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="D18" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="52" t="e">
+      <c r="E18" s="52" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="F16" s="52" t="e">
+      <c r="F18" s="52" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="52" t="e">
+      <c r="G18" s="52" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="H16" s="53">
+      <c r="H18" s="53">
         <v>2</v>
       </c>
-      <c r="I16" s="53">
+      <c r="I18" s="53">
         <v>14</v>
       </c>
-      <c r="J16" s="53">
+      <c r="J18" s="53">
         <v>3</v>
       </c>
-      <c r="K16" s="53">
+      <c r="K18" s="53">
         <v>7</v>
       </c>
-      <c r="L16" s="53">
+      <c r="L18" s="53">
         <v>11</v>
       </c>
-      <c r="M16" s="53">
+      <c r="M18" s="53">
         <v>10</v>
       </c>
-      <c r="N16" s="53">
+      <c r="N18" s="53">
         <v>19</v>
       </c>
-      <c r="O16" s="53">
+      <c r="O18" s="53">
         <v>2</v>
       </c>
-      <c r="P16" s="53">
+      <c r="P18" s="53">
         <v>16</v>
       </c>
-      <c r="R16" s="53">
+      <c r="R18" s="53">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="R17" s="53">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="R19" s="53">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="R18" s="53">
+    <row r="20" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="R20" s="53">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="R19" s="53">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="R21" s="53">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="R20" s="53">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="R22" s="53">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="R21" s="53">
+    <row r="23" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="R23" s="53">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="R22" s="53">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="R24" s="53">
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C24" s="12" t="s">
+    <row r="26" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C26" s="12" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C25" s="53">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C27" s="53">
         <v>1</v>
       </c>
-      <c r="D25" s="56" t="s">
+      <c r="D27" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="16" cm="1">
-        <f t="array" ref="E25:P25" xml:space="preserve"> RXL_RCalc(E$10:P$10, C25)</f>
+      <c r="E27" s="58" cm="1">
+        <f t="array" ref="E27:P27" xml:space="preserve"> RXL_RCalc(E$12:P$12, C27)</f>
         <v>6</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F27" s="16">
         <v>15</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G27" s="16">
         <v>26</v>
       </c>
-      <c r="H25" s="16">
+      <c r="H27" s="16">
         <v>28</v>
       </c>
-      <c r="I25" s="16">
+      <c r="I27" s="16">
         <v>42</v>
       </c>
-      <c r="J25" s="16">
+      <c r="J27" s="16">
         <v>45</v>
       </c>
-      <c r="K25" s="16">
+      <c r="K27" s="16">
         <v>52</v>
       </c>
-      <c r="L25" s="16">
+      <c r="L27" s="16">
         <v>63</v>
       </c>
-      <c r="M25" s="16">
+      <c r="M27" s="16">
         <v>73</v>
       </c>
-      <c r="N25" s="16">
+      <c r="N27" s="16">
         <v>92</v>
       </c>
-      <c r="O25" s="16">
+      <c r="O27" s="16">
         <v>94</v>
       </c>
-      <c r="P25" s="16">
+      <c r="P27" s="16">
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C26" s="53">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C28" s="53">
         <v>2</v>
       </c>
-      <c r="D26" s="56" t="s">
+      <c r="D28" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="16" cm="1">
-        <f t="array" ref="E26:P26" xml:space="preserve"> RXL_RCalc(E$10:P$10, C26)</f>
+      <c r="E28" s="58" cm="1">
+        <f t="array" ref="E28:P28" xml:space="preserve"> RXL_RCalc(E$12:P$12, C28)</f>
         <v>1</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F28" s="16">
         <v>2</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G28" s="16">
         <v>3</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H28" s="16">
         <v>4</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I28" s="16">
         <v>5</v>
       </c>
-      <c r="J26" s="16">
+      <c r="J28" s="16">
         <v>6</v>
       </c>
-      <c r="K26" s="16">
+      <c r="K28" s="16">
         <v>7</v>
       </c>
-      <c r="L26" s="16">
+      <c r="L28" s="16">
         <v>8</v>
       </c>
-      <c r="M26" s="16">
+      <c r="M28" s="16">
         <v>9</v>
       </c>
-      <c r="N26" s="16">
+      <c r="N28" s="16">
         <v>10</v>
       </c>
-      <c r="O26" s="16">
+      <c r="O28" s="16">
         <v>11</v>
       </c>
-      <c r="P26" s="16">
+      <c r="P28" s="16">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C27" s="53">
+    <row r="29" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C29" s="53">
         <v>3</v>
       </c>
-      <c r="D27" s="56" t="s">
+      <c r="D29" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="E27" s="16" cm="1">
-        <f t="array" ref="E27:P27" xml:space="preserve"> RXL_RCalc(E$10:P$10, C27)</f>
+      <c r="E29" s="58" cm="1">
+        <f t="array" ref="E29:P29" xml:space="preserve"> RXL_RCalc(E$12:P$12, C29)</f>
         <v>6</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F29" s="16">
         <v>7.5</v>
       </c>
-      <c r="G27" s="16">
+      <c r="G29" s="16">
         <v>8.6666666666666661</v>
       </c>
-      <c r="H27" s="16">
+      <c r="H29" s="16">
         <v>7</v>
       </c>
-      <c r="I27" s="16">
+      <c r="I29" s="16">
         <v>8.4</v>
       </c>
-      <c r="J27" s="16">
+      <c r="J29" s="16">
         <v>7.5</v>
       </c>
-      <c r="K27" s="16">
+      <c r="K29" s="16">
         <v>7.4285714285714288</v>
       </c>
-      <c r="L27" s="16">
+      <c r="L29" s="16">
         <v>7.875</v>
       </c>
-      <c r="M27" s="16">
+      <c r="M29" s="16">
         <v>8.1111111111111107</v>
       </c>
-      <c r="N27" s="16">
+      <c r="N29" s="16">
         <v>9.1999999999999993</v>
       </c>
-      <c r="O27" s="16">
+      <c r="O29" s="16">
         <v>8.545454545454545</v>
       </c>
-      <c r="P27" s="16">
+      <c r="P29" s="16">
         <v>9.1666666666666661</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C28" s="53">
+    <row r="30" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C30" s="53">
         <v>4</v>
       </c>
-      <c r="D28" s="56" t="s">
+      <c r="D30" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="16" cm="1">
-        <f t="array" ref="E28:P28" xml:space="preserve"> RXL_RCalc(E$10:P$10, C28)</f>
+      <c r="E30" s="58" cm="1">
+        <f t="array" ref="E30:P30" xml:space="preserve"> RXL_RCalc(E$12:P$12, C30)</f>
         <v>6</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F30" s="16">
         <v>6</v>
       </c>
-      <c r="G28" s="16">
+      <c r="G30" s="16">
         <v>6</v>
       </c>
-      <c r="H28" s="16">
+      <c r="H30" s="16">
         <v>2</v>
       </c>
-      <c r="I28" s="16">
+      <c r="I30" s="16">
         <v>2</v>
       </c>
-      <c r="J28" s="16">
+      <c r="J30" s="16">
         <v>2</v>
       </c>
-      <c r="K28" s="16">
+      <c r="K30" s="16">
         <v>2</v>
       </c>
-      <c r="L28" s="16">
+      <c r="L30" s="16">
         <v>2</v>
       </c>
-      <c r="M28" s="16">
+      <c r="M30" s="16">
         <v>2</v>
       </c>
-      <c r="N28" s="16">
+      <c r="N30" s="16">
         <v>2</v>
       </c>
-      <c r="O28" s="16">
+      <c r="O30" s="16">
         <v>2</v>
       </c>
-      <c r="P28" s="16">
+      <c r="P30" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C29" s="53">
+    <row r="31" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C31" s="53">
         <v>5</v>
       </c>
-      <c r="D29" s="56" t="s">
+      <c r="D31" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="E29" s="16" cm="1">
-        <f t="array" ref="E29:P29" xml:space="preserve"> RXL_RCalc(E$10:P$10, C29)</f>
+      <c r="E31" s="58" cm="1">
+        <f t="array" ref="E31:P31" xml:space="preserve"> RXL_RCalc(E$12:P$12, C31)</f>
         <v>6</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F31" s="16">
         <v>9</v>
       </c>
-      <c r="G29" s="16">
+      <c r="G31" s="16">
         <v>11</v>
       </c>
-      <c r="H29" s="16">
+      <c r="H31" s="16">
         <v>11</v>
       </c>
-      <c r="I29" s="16">
+      <c r="I31" s="16">
         <v>14</v>
       </c>
-      <c r="J29" s="16">
+      <c r="J31" s="16">
         <v>14</v>
       </c>
-      <c r="K29" s="16">
+      <c r="K31" s="16">
         <v>14</v>
       </c>
-      <c r="L29" s="16">
+      <c r="L31" s="16">
         <v>14</v>
       </c>
-      <c r="M29" s="16">
+      <c r="M31" s="16">
         <v>14</v>
       </c>
-      <c r="N29" s="16">
+      <c r="N31" s="16">
         <v>19</v>
       </c>
-      <c r="O29" s="16">
+      <c r="O31" s="16">
         <v>19</v>
       </c>
-      <c r="P29" s="16">
+      <c r="P31" s="16">
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="E30" s="17" t="str">
-        <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(E25)</f>
-        <v>= RXL_RCalc(E$10:P$10, C25)</v>
-      </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C32" s="12" t="s">
+    <row r="32" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="E32" s="17" t="str">
+        <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(E27)</f>
+        <v>= RXL_RCalc(E$12:P$12, C27)</v>
+      </c>
+    </row>
+    <row r="34" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C34" s="12" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="33" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C33" s="53">
+    <row r="35" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C35" s="53">
         <v>1</v>
       </c>
-      <c r="D33" s="56" t="s">
+      <c r="D35" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="E33" s="16" cm="1">
-        <f t="array" ref="E33:P33" xml:space="preserve"> RXL_RCalc(E$11:P$11, D33)</f>
+      <c r="E35" s="58" cm="1">
+        <f t="array" ref="E35:P35" xml:space="preserve"> RXL_RCalc(E$13:P$13, D35)</f>
         <v>6</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F35" s="16">
         <v>15</v>
       </c>
-      <c r="G33" s="16">
+      <c r="G35" s="16">
         <v>15</v>
       </c>
-      <c r="H33" s="16">
+      <c r="H35" s="16">
         <v>17</v>
       </c>
-      <c r="I33" s="16">
+      <c r="I35" s="16">
         <v>31</v>
       </c>
-      <c r="J33" s="16">
+      <c r="J35" s="16">
         <v>34</v>
       </c>
-      <c r="K33" s="16">
+      <c r="K35" s="16">
         <v>41</v>
       </c>
-      <c r="L33" s="16">
+      <c r="L35" s="16">
         <v>52</v>
       </c>
-      <c r="M33" s="16">
+      <c r="M35" s="16">
         <v>62</v>
       </c>
-      <c r="N33" s="16">
+      <c r="N35" s="16">
         <v>81</v>
       </c>
-      <c r="O33" s="16">
+      <c r="O35" s="16">
         <v>83</v>
       </c>
-      <c r="P33" s="16">
+      <c r="P35" s="16">
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C34" s="53">
+    <row r="36" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C36" s="53">
         <v>2</v>
       </c>
-      <c r="D34" s="56" t="s">
+      <c r="D36" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="16" cm="1">
-        <f t="array" ref="E34:P34" xml:space="preserve"> RXL_RCalc(E$11:P$11, D34)</f>
+      <c r="E36" s="58" cm="1">
+        <f t="array" ref="E36:P36" xml:space="preserve"> RXL_RCalc(E$13:P$13, D36)</f>
         <v>1</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F36" s="16">
         <v>2</v>
       </c>
-      <c r="G34" s="16">
+      <c r="G36" s="16">
         <v>2</v>
       </c>
-      <c r="H34" s="16">
+      <c r="H36" s="16">
         <v>3</v>
       </c>
-      <c r="I34" s="16">
+      <c r="I36" s="16">
         <v>4</v>
       </c>
-      <c r="J34" s="16">
+      <c r="J36" s="16">
         <v>5</v>
       </c>
-      <c r="K34" s="16">
+      <c r="K36" s="16">
         <v>6</v>
       </c>
-      <c r="L34" s="16">
+      <c r="L36" s="16">
         <v>7</v>
       </c>
-      <c r="M34" s="16">
+      <c r="M36" s="16">
         <v>8</v>
       </c>
-      <c r="N34" s="16">
+      <c r="N36" s="16">
         <v>9</v>
       </c>
-      <c r="O34" s="16">
+      <c r="O36" s="16">
         <v>10</v>
       </c>
-      <c r="P34" s="16">
+      <c r="P36" s="16">
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C35" s="53">
+    <row r="37" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C37" s="53">
         <v>3</v>
       </c>
-      <c r="D35" s="56" t="s">
+      <c r="D37" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="16" cm="1">
-        <f t="array" ref="E35:P35" xml:space="preserve"> RXL_RCalc(E$11:P$11, D35)</f>
+      <c r="E37" s="58" cm="1">
+        <f t="array" ref="E37:P37" xml:space="preserve"> RXL_RCalc(E$13:P$13, D37)</f>
         <v>6</v>
       </c>
-      <c r="F35" s="16">
+      <c r="F37" s="16">
         <v>7.5</v>
       </c>
-      <c r="G35" s="16">
+      <c r="G37" s="16">
         <v>7.5</v>
       </c>
-      <c r="H35" s="16">
+      <c r="H37" s="16">
         <v>5.666666666666667</v>
       </c>
-      <c r="I35" s="16">
+      <c r="I37" s="16">
         <v>7.75</v>
       </c>
-      <c r="J35" s="16">
+      <c r="J37" s="16">
         <v>6.8</v>
       </c>
-      <c r="K35" s="16">
+      <c r="K37" s="16">
         <v>6.833333333333333</v>
       </c>
-      <c r="L35" s="16">
+      <c r="L37" s="16">
         <v>7.4285714285714288</v>
       </c>
-      <c r="M35" s="16">
+      <c r="M37" s="16">
         <v>7.75</v>
       </c>
-      <c r="N35" s="16">
+      <c r="N37" s="16">
         <v>9</v>
       </c>
-      <c r="O35" s="16">
+      <c r="O37" s="16">
         <v>8.3000000000000007</v>
       </c>
-      <c r="P35" s="16">
+      <c r="P37" s="16">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C36" s="53">
+    <row r="38" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C38" s="53">
         <v>4</v>
       </c>
-      <c r="D36" s="56" t="s">
+      <c r="D38" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="E36" s="16" cm="1">
-        <f t="array" ref="E36:P36" xml:space="preserve"> RXL_RCalc(E$11:P$11, D36)</f>
+      <c r="E38" s="58" cm="1">
+        <f t="array" ref="E38:P38" xml:space="preserve"> RXL_RCalc(E$13:P$13, D38)</f>
         <v>6</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F38" s="16">
         <v>6</v>
       </c>
-      <c r="G36" s="16">
+      <c r="G38" s="16">
         <v>6</v>
       </c>
-      <c r="H36" s="16">
+      <c r="H38" s="16">
         <v>2</v>
       </c>
-      <c r="I36" s="16">
+      <c r="I38" s="16">
         <v>2</v>
       </c>
-      <c r="J36" s="16">
+      <c r="J38" s="16">
         <v>2</v>
       </c>
-      <c r="K36" s="16">
+      <c r="K38" s="16">
         <v>2</v>
       </c>
-      <c r="L36" s="16">
+      <c r="L38" s="16">
         <v>2</v>
       </c>
-      <c r="M36" s="16">
+      <c r="M38" s="16">
         <v>2</v>
       </c>
-      <c r="N36" s="16">
+      <c r="N38" s="16">
         <v>2</v>
       </c>
-      <c r="O36" s="16">
+      <c r="O38" s="16">
         <v>2</v>
       </c>
-      <c r="P36" s="16">
+      <c r="P38" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C37" s="53">
+    <row r="39" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C39" s="53">
         <v>5</v>
       </c>
-      <c r="D37" s="56" t="s">
+      <c r="D39" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="E37" s="16" cm="1">
-        <f t="array" ref="E37:P37" xml:space="preserve"> RXL_RCalc(E$11:P$11, D37)</f>
+      <c r="E39" s="58" cm="1">
+        <f t="array" ref="E39:P39" xml:space="preserve"> RXL_RCalc(E$13:P$13, D39)</f>
         <v>6</v>
       </c>
-      <c r="F37" s="16">
+      <c r="F39" s="16">
         <v>9</v>
       </c>
-      <c r="G37" s="16">
+      <c r="G39" s="16">
         <v>9</v>
       </c>
-      <c r="H37" s="16">
+      <c r="H39" s="16">
         <v>9</v>
       </c>
-      <c r="I37" s="16">
+      <c r="I39" s="16">
         <v>14</v>
       </c>
-      <c r="J37" s="16">
+      <c r="J39" s="16">
         <v>14</v>
       </c>
-      <c r="K37" s="16">
+      <c r="K39" s="16">
         <v>14</v>
       </c>
-      <c r="L37" s="16">
+      <c r="L39" s="16">
         <v>14</v>
       </c>
-      <c r="M37" s="16">
+      <c r="M39" s="16">
         <v>14</v>
       </c>
-      <c r="N37" s="16">
+      <c r="N39" s="16">
         <v>19</v>
       </c>
-      <c r="O37" s="16">
+      <c r="O39" s="16">
         <v>19</v>
       </c>
-      <c r="P37" s="16">
+      <c r="P39" s="16">
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="E38" s="17" t="str">
-        <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(E33)</f>
-        <v>= RXL_RCalc(E$11:P$11, D33)</v>
-      </c>
-    </row>
-    <row r="40" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C40" s="12" t="s">
+    <row r="40" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="E40" s="17" t="str">
+        <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(E35)</f>
+        <v>= RXL_RCalc(E$13:P$13, D35)</v>
+      </c>
+    </row>
+    <row r="42" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C42" s="12" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="41" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="D41" s="21" t="s">
+    <row r="43" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="D43" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="E41" s="53" t="b">
+      <c r="E43" s="53" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="D42" s="21" t="s">
+    <row r="44" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="D44" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="E42" s="53" t="b">
+      <c r="E44" s="53" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C43" s="53">
+    <row r="45" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C45" s="53">
         <v>1</v>
       </c>
-      <c r="D43" s="56" t="s">
+      <c r="D45" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="E43" s="16" cm="1">
-        <f t="array" ref="E43:P43" xml:space="preserve"> RXL_RCalc(E$13:P$13, D43, E$41, E$42)</f>
+      <c r="E45" s="58" cm="1">
+        <f t="array" ref="E45:P45" xml:space="preserve"> RXL_RCalc(E$15:P$15, D45, E$43, E$44)</f>
         <v>6</v>
       </c>
-      <c r="F43" s="16">
+      <c r="F45" s="16">
         <v>15</v>
       </c>
-      <c r="G43" s="16">
+      <c r="G45" s="16">
         <v>15</v>
       </c>
-      <c r="H43" s="16">
+      <c r="H45" s="16">
         <v>15</v>
       </c>
-      <c r="I43" s="16">
+      <c r="I45" s="16">
         <v>29</v>
       </c>
-      <c r="J43" s="16">
+      <c r="J45" s="16">
         <v>29</v>
       </c>
-      <c r="K43" s="16">
+      <c r="K45" s="16">
         <v>36</v>
       </c>
-      <c r="L43" s="16">
+      <c r="L45" s="16">
         <v>36</v>
       </c>
-      <c r="M43" s="16">
+      <c r="M45" s="16">
         <v>46</v>
       </c>
-      <c r="N43" s="16">
+      <c r="N45" s="16">
         <v>65</v>
       </c>
-      <c r="O43" s="16">
+      <c r="O45" s="16">
         <v>67</v>
       </c>
-      <c r="P43" s="16">
+      <c r="P45" s="16">
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C44" s="53">
+    <row r="46" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C46" s="53">
         <v>2</v>
       </c>
-      <c r="D44" s="56" t="s">
+      <c r="D46" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="E44" s="16" cm="1">
-        <f t="array" ref="E44:P44" xml:space="preserve"> RXL_RCalc(E$13:P$13, D44, E$41, E$42)</f>
+      <c r="E46" s="58" cm="1">
+        <f t="array" ref="E46:P46" xml:space="preserve"> RXL_RCalc(E$15:P$15, D46, E$43, E$44)</f>
         <v>1</v>
       </c>
-      <c r="F44" s="16">
+      <c r="F46" s="16">
         <v>2</v>
       </c>
-      <c r="G44" s="16">
+      <c r="G46" s="16">
         <v>2</v>
       </c>
-      <c r="H44" s="16">
+      <c r="H46" s="16">
         <v>2</v>
       </c>
-      <c r="I44" s="16">
+      <c r="I46" s="16">
         <v>3</v>
       </c>
-      <c r="J44" s="16">
+      <c r="J46" s="16">
         <v>3</v>
       </c>
-      <c r="K44" s="16">
+      <c r="K46" s="16">
         <v>4</v>
       </c>
-      <c r="L44" s="16">
+      <c r="L46" s="16">
         <v>4</v>
       </c>
-      <c r="M44" s="16">
+      <c r="M46" s="16">
         <v>5</v>
-      </c>
-      <c r="N44" s="16">
-        <v>6</v>
-      </c>
-      <c r="O44" s="16">
-        <v>7</v>
-      </c>
-      <c r="P44" s="16">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C45" s="53">
-        <v>3</v>
-      </c>
-      <c r="D45" s="56" t="s">
-        <v>33</v>
-      </c>
-      <c r="E45" s="16" cm="1">
-        <f t="array" ref="E45:P45" xml:space="preserve"> RXL_RCalc(E$13:P$13, D45, E$41, E$42)</f>
-        <v>6</v>
-      </c>
-      <c r="F45" s="16">
-        <v>7.5</v>
-      </c>
-      <c r="G45" s="16">
-        <v>7.5</v>
-      </c>
-      <c r="H45" s="16">
-        <v>7.5</v>
-      </c>
-      <c r="I45" s="16">
-        <v>9.6666666666666661</v>
-      </c>
-      <c r="J45" s="16">
-        <v>9.6666666666666661</v>
-      </c>
-      <c r="K45" s="16">
-        <v>9</v>
-      </c>
-      <c r="L45" s="16">
-        <v>9</v>
-      </c>
-      <c r="M45" s="16">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="N45" s="16">
-        <v>10.833333333333334</v>
-      </c>
-      <c r="O45" s="16">
-        <v>9.5714285714285712</v>
-      </c>
-      <c r="P45" s="16">
-        <v>10.375</v>
-      </c>
-    </row>
-    <row r="46" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C46" s="53">
-        <v>4</v>
-      </c>
-      <c r="D46" s="56" t="s">
-        <v>31</v>
-      </c>
-      <c r="E46" s="16" cm="1">
-        <f t="array" ref="E46:P46" xml:space="preserve"> RXL_RCalc(E$13:P$13, D46, E$41, E$42)</f>
-        <v>6</v>
-      </c>
-      <c r="F46" s="16">
-        <v>6</v>
-      </c>
-      <c r="G46" s="16">
-        <v>6</v>
-      </c>
-      <c r="H46" s="16">
-        <v>6</v>
-      </c>
-      <c r="I46" s="16">
-        <v>6</v>
-      </c>
-      <c r="J46" s="16">
-        <v>6</v>
-      </c>
-      <c r="K46" s="16">
-        <v>6</v>
-      </c>
-      <c r="L46" s="16">
-        <v>6</v>
-      </c>
-      <c r="M46" s="16">
-        <v>6</v>
       </c>
       <c r="N46" s="16">
         <v>6</v>
       </c>
       <c r="O46" s="16">
+        <v>7</v>
+      </c>
+      <c r="P46" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C47" s="53">
+        <v>3</v>
+      </c>
+      <c r="D47" s="56" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" s="58" cm="1">
+        <f t="array" ref="E47:P47" xml:space="preserve"> RXL_RCalc(E$15:P$15, D47, E$43, E$44)</f>
+        <v>6</v>
+      </c>
+      <c r="F47" s="16">
+        <v>7.5</v>
+      </c>
+      <c r="G47" s="16">
+        <v>7.5</v>
+      </c>
+      <c r="H47" s="16">
+        <v>7.5</v>
+      </c>
+      <c r="I47" s="16">
+        <v>9.6666666666666661</v>
+      </c>
+      <c r="J47" s="16">
+        <v>9.6666666666666661</v>
+      </c>
+      <c r="K47" s="16">
+        <v>9</v>
+      </c>
+      <c r="L47" s="16">
+        <v>9</v>
+      </c>
+      <c r="M47" s="16">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="N47" s="16">
+        <v>10.833333333333334</v>
+      </c>
+      <c r="O47" s="16">
+        <v>9.5714285714285712</v>
+      </c>
+      <c r="P47" s="16">
+        <v>10.375</v>
+      </c>
+    </row>
+    <row r="48" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C48" s="53">
+        <v>4</v>
+      </c>
+      <c r="D48" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" s="58" cm="1">
+        <f t="array" ref="E48:P48" xml:space="preserve"> RXL_RCalc(E$15:P$15, D48, E$43, E$44)</f>
+        <v>6</v>
+      </c>
+      <c r="F48" s="16">
+        <v>6</v>
+      </c>
+      <c r="G48" s="16">
+        <v>6</v>
+      </c>
+      <c r="H48" s="16">
+        <v>6</v>
+      </c>
+      <c r="I48" s="16">
+        <v>6</v>
+      </c>
+      <c r="J48" s="16">
+        <v>6</v>
+      </c>
+      <c r="K48" s="16">
+        <v>6</v>
+      </c>
+      <c r="L48" s="16">
+        <v>6</v>
+      </c>
+      <c r="M48" s="16">
+        <v>6</v>
+      </c>
+      <c r="N48" s="16">
+        <v>6</v>
+      </c>
+      <c r="O48" s="16">
         <v>2</v>
       </c>
-      <c r="P46" s="16">
+      <c r="P48" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C47" s="53">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C49" s="53">
         <v>5</v>
       </c>
-      <c r="D47" s="56" t="s">
+      <c r="D49" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="E47" s="16" cm="1">
-        <f t="array" ref="E47:P47" xml:space="preserve"> RXL_RCalc(E$13:P$13, D47, E$41, E$42)</f>
+      <c r="E49" s="58" cm="1">
+        <f t="array" ref="E49:P49" xml:space="preserve"> RXL_RCalc(E$15:P$15, D49, E$43, E$44)</f>
         <v>6</v>
       </c>
-      <c r="F47" s="16">
+      <c r="F49" s="16">
         <v>9</v>
       </c>
-      <c r="G47" s="16">
+      <c r="G49" s="16">
         <v>9</v>
       </c>
-      <c r="H47" s="16">
+      <c r="H49" s="16">
         <v>9</v>
       </c>
-      <c r="I47" s="16">
+      <c r="I49" s="16">
         <v>14</v>
       </c>
-      <c r="J47" s="16">
+      <c r="J49" s="16">
         <v>14</v>
       </c>
-      <c r="K47" s="16">
+      <c r="K49" s="16">
         <v>14</v>
       </c>
-      <c r="L47" s="16">
+      <c r="L49" s="16">
         <v>14</v>
       </c>
-      <c r="M47" s="16">
+      <c r="M49" s="16">
         <v>14</v>
       </c>
-      <c r="N47" s="16">
+      <c r="N49" s="16">
         <v>19</v>
       </c>
-      <c r="O47" s="16">
+      <c r="O49" s="16">
         <v>19</v>
       </c>
-      <c r="P47" s="16">
+      <c r="P49" s="16">
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="E48" s="17" t="str">
-        <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(E43)</f>
-        <v>= RXL_RCalc(E$13:P$13, D43, E$41, E$42)</v>
-      </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C51" s="12" t="s">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="E50" s="17" t="str">
+        <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(E45)</f>
+        <v>= RXL_RCalc(E$15:P$15, D45, E$43, E$44)</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C53" s="12" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="D52" s="56" t="s">
+    <row r="54" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="D54" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="E52" s="16" cm="1">
-        <f t="array" ref="E52:P52" xml:space="preserve"> RXL_RCalc(E$10:P$10, D52)</f>
+      <c r="E54" s="58" cm="1">
+        <f t="array" ref="E54:P54" xml:space="preserve"> RXL_RCalc(E$12:P$12, D54)</f>
         <v>6</v>
       </c>
-      <c r="F52" s="16">
+      <c r="F54" s="16">
         <v>15</v>
       </c>
-      <c r="G52" s="16">
+      <c r="G54" s="16">
         <v>26</v>
       </c>
-      <c r="H52" s="16">
+      <c r="H54" s="16">
         <v>28</v>
       </c>
-      <c r="I52" s="16">
+      <c r="I54" s="16">
         <v>42</v>
       </c>
-      <c r="J52" s="16">
+      <c r="J54" s="16">
         <v>45</v>
       </c>
-      <c r="K52" s="16">
+      <c r="K54" s="16">
         <v>52</v>
       </c>
-      <c r="L52" s="16">
+      <c r="L54" s="16">
         <v>63</v>
       </c>
-      <c r="M52" s="16">
+      <c r="M54" s="16">
         <v>73</v>
       </c>
-      <c r="N52" s="16">
+      <c r="N54" s="16">
         <v>92</v>
       </c>
-      <c r="O52" s="16">
+      <c r="O54" s="16">
         <v>94</v>
       </c>
-      <c r="P52" s="16">
+      <c r="P54" s="16">
         <v>110</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="E53" s="17" t="str">
-        <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(E52)</f>
-        <v>= RXL_RCalc(E$10:P$10, D52)</v>
-      </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="D55" s="21" t="s">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="E55" s="17" t="str">
+        <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(E54)</f>
+        <v>= RXL_RCalc(E$12:P$12, D54)</v>
+      </c>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="D57" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="E55" s="53" t="b">
+      <c r="E57" s="53" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="D56" s="56" t="s">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="D58" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="E56" s="16" cm="1">
-        <f t="array" ref="E56:P56" xml:space="preserve"> RXL_RCalc(E$10:P$10, D56, , , E55)</f>
+      <c r="E58" s="58" cm="1">
+        <f t="array" ref="E58:P58" xml:space="preserve"> RXL_RCalc(E$12:P$12, D58, , , E57)</f>
         <v>6</v>
       </c>
-      <c r="F56" s="16">
+      <c r="F58" s="16">
         <v>15</v>
       </c>
-      <c r="G56" s="16">
+      <c r="G58" s="16">
         <v>26</v>
       </c>
-      <c r="H56" s="16">
+      <c r="H58" s="16">
         <v>28</v>
       </c>
-      <c r="I56" s="16">
+      <c r="I58" s="16">
         <v>42</v>
       </c>
-      <c r="J56" s="16">
+      <c r="J58" s="16">
         <v>45</v>
       </c>
-      <c r="K56" s="16">
+      <c r="K58" s="16">
         <v>52</v>
       </c>
-      <c r="L56" s="16">
+      <c r="L58" s="16">
         <v>63</v>
       </c>
-      <c r="M56" s="16">
+      <c r="M58" s="16">
         <v>73</v>
       </c>
-      <c r="N56" s="16">
+      <c r="N58" s="16">
         <v>92</v>
       </c>
-      <c r="O56" s="16">
+      <c r="O58" s="16">
         <v>94</v>
       </c>
-      <c r="P56" s="16">
+      <c r="P58" s="16">
         <v>110</v>
       </c>
     </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="E57" s="16"/>
-      <c r="F57" s="17" t="str">
-        <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(E56)</f>
-        <v>= RXL_RCalc(E$10:P$10, D56, , , E55)</v>
-      </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="E58" s="16"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.3">
       <c r="E59" s="16"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="F59" s="17" t="str">
+        <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(E58)</f>
+        <v>= RXL_RCalc(E$12:P$12, D58, , , E57)</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.3">
       <c r="E60" s="16"/>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.3">
       <c r="E61" s="16"/>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.3">
       <c r="E62" s="16"/>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.3">
       <c r="E63" s="16"/>
     </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:16" x14ac:dyDescent="0.3">
       <c r="E64" s="16"/>
     </row>
-    <row r="65" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="65" spans="3:18" x14ac:dyDescent="0.3">
       <c r="E65" s="16"/>
     </row>
-    <row r="66" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="66" spans="3:18" x14ac:dyDescent="0.3">
       <c r="E66" s="16"/>
     </row>
-    <row r="67" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="3:18" x14ac:dyDescent="0.3">
       <c r="E67" s="16"/>
     </row>
-    <row r="68" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="68" spans="3:18" x14ac:dyDescent="0.3">
       <c r="E68" s="16"/>
     </row>
-    <row r="70" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="C70" s="12" t="s">
+    <row r="69" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="E69" s="16"/>
+    </row>
+    <row r="70" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="E70" s="16"/>
+    </row>
+    <row r="72" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C72" s="12" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="71" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="D71" s="56" t="s">
+    <row r="73" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="D73" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="F71" s="21" t="s">
+      <c r="F73" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="G71" s="53" t="b">
+      <c r="G73" s="53" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="D72" s="16" cm="1">
-        <f t="array" ref="D72:D83" xml:space="preserve"> RXL_RCalc($R$11:$R$22, D71)</f>
+    <row r="74" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="D74" s="58" cm="1">
+        <f t="array" ref="D74:D85" xml:space="preserve"> RXL_RCalc($R$13:$R$24, D73)</f>
         <v>6</v>
       </c>
-      <c r="F72" s="56" t="s">
+      <c r="F74" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="G72" s="16" cm="1">
-        <f t="array" ref="G72:G83" xml:space="preserve"> RXL_RCalc($R$11:$R$22, F72, , , G71)</f>
+      <c r="G74" s="58" cm="1">
+        <f t="array" ref="G74:G85" xml:space="preserve"> RXL_RCalc($R$13:$R$24, F74, , , G73)</f>
         <v>6</v>
       </c>
-      <c r="H72" s="16"/>
-      <c r="I72" s="16"/>
-      <c r="J72" s="16"/>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="16"/>
-      <c r="O72" s="16"/>
-      <c r="P72" s="16"/>
-      <c r="Q72" s="16"/>
-      <c r="R72" s="16"/>
-    </row>
-    <row r="73" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="D73" s="16">
+      <c r="H74" s="16"/>
+      <c r="I74" s="16"/>
+      <c r="J74" s="16"/>
+      <c r="K74" s="16"/>
+      <c r="L74" s="16"/>
+      <c r="M74" s="16"/>
+      <c r="N74" s="16"/>
+      <c r="O74" s="16"/>
+      <c r="P74" s="16"/>
+      <c r="Q74" s="16"/>
+      <c r="R74" s="16"/>
+    </row>
+    <row r="75" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="D75" s="16">
         <v>15</v>
       </c>
-      <c r="G73" s="16">
+      <c r="G75" s="16">
         <v>15</v>
       </c>
-      <c r="H73" s="17" t="str">
-        <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(G72)</f>
-        <v>= RXL_RCalc($R$11:$R$22, F72, , , G71)</v>
-      </c>
-    </row>
-    <row r="74" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="D74" s="16">
+      <c r="H75" s="17" t="str">
+        <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(G74)</f>
+        <v>= RXL_RCalc($R$13:$R$24, F74, , , G73)</v>
+      </c>
+    </row>
+    <row r="76" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="D76" s="16">
         <v>26</v>
       </c>
-      <c r="G74" s="16">
+      <c r="G76" s="16">
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="D75" s="16">
+    <row r="77" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="D77" s="16">
         <v>28</v>
       </c>
-      <c r="G75" s="16">
+      <c r="G77" s="16">
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="D76" s="16">
+    <row r="78" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="D78" s="16">
         <v>42</v>
       </c>
-      <c r="G76" s="16">
+      <c r="G78" s="16">
         <v>42</v>
       </c>
     </row>
-    <row r="77" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="D77" s="16">
+    <row r="79" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="D79" s="16">
         <v>45</v>
       </c>
-      <c r="G77" s="16">
+      <c r="G79" s="16">
         <v>45</v>
       </c>
     </row>
-    <row r="78" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="D78" s="16">
+    <row r="80" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="D80" s="16">
         <v>52</v>
       </c>
-      <c r="G78" s="16">
+      <c r="G80" s="16">
         <v>52</v>
       </c>
     </row>
-    <row r="79" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="D79" s="16">
+    <row r="81" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D81" s="16">
         <v>63</v>
       </c>
-      <c r="G79" s="16">
+      <c r="G81" s="16">
         <v>63</v>
       </c>
     </row>
-    <row r="80" spans="3:18" x14ac:dyDescent="0.2">
-      <c r="D80" s="16">
+    <row r="82" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D82" s="16">
         <v>73</v>
       </c>
-      <c r="G80" s="16">
+      <c r="G82" s="16">
         <v>73</v>
       </c>
     </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D81" s="16">
+    <row r="83" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D83" s="16">
         <v>92</v>
       </c>
-      <c r="G81" s="16">
+      <c r="G83" s="16">
         <v>92</v>
       </c>
     </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D82" s="16">
+    <row r="84" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D84" s="16">
         <v>94</v>
       </c>
-      <c r="G82" s="16">
+      <c r="G84" s="16">
         <v>94</v>
       </c>
     </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D83" s="16">
+    <row r="85" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D85" s="16">
         <v>110</v>
       </c>
-      <c r="G83" s="16">
+      <c r="G85" s="16">
         <v>110</v>
       </c>
     </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D84" s="17" t="str">
-        <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(D72)</f>
-        <v>= RXL_RCalc($R$11:$R$22, D71)</v>
-      </c>
-    </row>
-    <row r="86" spans="2:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="2:7" s="57" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="57" t="s">
+    <row r="86" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D86" s="17" t="str">
+        <f ca="1" xml:space="preserve"> _xlfn.FORMULATEXT(D74)</f>
+        <v>= RXL_RCalc($R$13:$R$24, D73)</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="89" spans="2:7" s="57" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B89" s="57" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E6" r:id="rId1" xr:uid="{7B68C5A8-FA14-4A01-AFC0-0D2AA3A09C22}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82A8A26C-6D39-4C1B-AF2B-075D27C91DD7}">
+  <sheetPr codeName="Sheet13"/>
+  <dimension ref="B1:C110"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="4.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3" s="4" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="5">
+        <f xml:space="preserve"> MAX(B$1:B1) + 1</f>
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B6" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="C6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B7" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="C17" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B38" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="C38" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B39" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="C39" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C40" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B64" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="C64" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" s="4" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B71" s="5">
+        <f xml:space="preserve"> MAX(B$1:B70) + 1</f>
+        <v>2</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C73" s="62" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C74" s="62"/>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C75" s="62" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C76" s="62" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C77" s="62" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C78" s="63" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C79" s="62" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C80" s="62" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C81" s="64" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C82" s="63" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C83" s="62" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C84" s="64" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C85" s="62" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="86" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C86" s="62" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C87" s="64" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C88" s="64" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="89" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C89" s="62" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="90" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C90" s="64" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C91" s="62" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C92" s="62" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="93" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C93" s="62" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="94" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C94" s="62" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="95" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C95" s="62" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="96" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C96" s="62" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C97" s="62" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C98" s="62" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C99" s="62" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C100" s="64" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C101" s="62" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C102" s="64" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C103" s="64" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C104" s="62" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C105" s="64" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C106" s="62" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C107" s="64" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="110" spans="2:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B110" s="2" t="s">
         <v>0</v>
       </c>
     </row>
@@ -11071,21 +12110,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F99A15E-3384-4194-A934-E1FDEF2D75BB}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="B1:D10"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="4.28515625" customWidth="1"/>
+    <col min="1" max="2" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:4" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C1" s="9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="8">
         <v>1</v>
       </c>
@@ -11093,7 +12132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="8">
         <v>0</v>
       </c>
@@ -11104,7 +12143,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="8">
         <v>1</v>
       </c>
@@ -11112,7 +12151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="8">
         <v>0</v>
       </c>
@@ -11123,8 +12162,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="2:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:4" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="2:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>0</v>
       </c>
@@ -11136,7 +12175,7 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgCjACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAGcAYgAiAH0AfQA=</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuAC8AKgAgACAAUgBYAEwAXwBSAEMAYQBsAGMAIABGAHUAbgBjAHQAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIAB2AGUAcgBzAGkAbwBuACAAMQAuADAANAAgACAAKAAwADQALQBKAHUAbgAtADIAMAAyADUAKQBcAG4AIAAgACAAIAAgACAAIAAgAFIAIABTAGkAbABrACwAIABSAFgATAAgAEQAZQB2AGUAbABvAHAAbQBlAG4AdABcAG4AIAAgACAAIAAgACAAIAAgAGgAdAB0AHAAcwA6AC8ALwBnAGkAcwB0AC4AZwBpAHQAaAB1AGIALgBjAG8AbQAvAHIALQBzAGkAbABrAC8AYgAxADIANABmADgANAA2ADgAYgAxADYAMQA1AGEANAAwAGIANAAyAGYAZQBkAGEANwA1ADQANQBiAGMAMABhAFwAbgAqAC8AXABuAC8AKgBcAG4AIAAgACAAIABOAGEAbQBlADoAIAAgACAAIAAgACAAIAAgAFIAQwBhAGwAYwAoACkAXABuACAAIAAgACAARABlAHMAYwByAGkAcAB0AGkAbwBuADoAIAAqAC8ALwAqACoAUABlAHIAZgBvAHIAbQBzACAAYQAgAHIAbwBsAGwAaQBuAGcAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AIABvAG4AIABhACAAMQBEACAAaQBuAHAAdQB0ACAAZABhAHQAYQAgAGEAcgByAGEAeQAqAC8ALwAqAFwAbgAgACAAIAAgAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIAAgACAAIAAgACsAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA9ACAAKAByAGUAcQB1AGkAcgBlAGQAKQAgAEEAbgAgAGEAcgByAGEAeQAgAG8AZgAgAHYAYQBsAHUAZQBzACAAdABvACAAYgBlACAAdQBzAGUAZAAgAGYAbwByACAAdABoAGUAIAByAG8AbABsAGkAbgBnACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuACAALQAtACAAbQB1AHMAdAAgAGIAZQAgAGEAIAAxAEQAIABhAHIAcgBhAHkALAAgAGkALgBlAC4AIABzAGkAbgBnAGwAZQAgAHIAbwB3ACAAbwByACAAcwBpAG4AZwBsAGUAIABjAG8AbAB1AG0AbgAgAG8AZgAgAGQAYQB0AGEAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGgAZQAgAGEAcgByAGEAeQAgAGMAYQBuACAAYgBlACAAcwB1AHAAcABsAGkAZQBkACAAYQBzACAAcgBvAHcAIABvAHIAIABjAG8AbAB1AG0AbgA6ACAAZgBvAHIAIABhACAAcgBvAHcAIABvAGYAIABkAGEAdABhACAAdABoAGUAIAByAG8AbABsAGkAbgBnACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuACAAdwBpAGwAbAAgAHIAZQBhAGQAIABmAHIAbwBtACAAbABlAGYAdAAgAHQAbwAgAHIAaQBnAGgAdABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAG8AcgAgAGEAIABjAG8AbAB1AG0AbgAgAG8AZgAgAGQAYQB0AGEAIAB0AGgAZQAgAHIAbwBsAGwAaQBuAGcAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AIAB3AGkAbABsACAAcgBlAGEAZAAgAGYAcgBvAG0AIAB0AG8AcAAgAHQAbwAgAGIAbwB0AHQAbwBtAFwAbgAgACAAIAAgACAAIAAgACAAKwAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAgACAAIAAgACAAIAAgAD0AIAAoAHIAZQBxAHUAaQByAGUAZAApACAAQQAgAHMAaQBuAGcAbABlACAAdgBhAGwAdQBlACAAKABuAHUAbQBiAGUAcgAgAG8AcgAgAHQAZQB4AHQAKQAgAHQAbwAgAHMAZQB0ACAAdABoAGUAIAB0AHkAcABlACAAbwBmACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuACAAdABvACAAYQBwAHAAbAB5ACAAdABvACAAdABoAGUAIABhAHIAcgBhAHkAIABvAGYAIABpAG4AcAB1AHQAIABkAGEAdABhAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVgBhAGwAaQBkACAAaQBuAHAAdQB0AHMAIABhAHIAZQAgAGEAIABuAHUAbQBiAGUAcgAgAGIAZQB0AHcAZQBlAG4AIAAxACAAYQBuAGQAIAA1ACAAbwByACAAYQAgAHYAYQBsAGkAZAAgAHQAZQB4AHQAIABzAHQAcgBpAG4AZwAgAGYAcgBvAG0AIAB0AGgAZQAgAGwAaQBzAHQAIABiAGUAbABvAHcAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxACAALwAgAFwAIgBzAHUAbQBcACIAIAAgACAAPQAgAHIAbwBsAGwAaQBuAGcAIABTAFUATQAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgADIAIAAvACAAXAAiAGMAbwB1AG4AdABcACIAIAA9ACAAcgBvAGwAbABpAG4AZwAgAGMAbwB1AG4AdAAgAG8AZgAgAG4AdQBtAGUAcgBpAGMAIAB2AGEAbAB1AGUAcwAgACgAQwBPAFUATgBUACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAzACAALwAgAFwAIgBhAHYAZwBcACIAIAAgACAAPQAgAHIAbwBsAGwAaQBuAGcAIABBAFYARQBSAEEARwBFACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAANAAgAC8AIABcACIAbQBpAG4AXAAiACAAIAAgAD0AIAByAG8AbABsAGkAbgBnACAATQBJAE4AIABjAGEAbABjAHUAbABhAHQAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAA1ACAALwAgAFwAIgBtAGEAeABcACIAIAAgACAAPQAgAHIAbwBsAGwAaQBuAGcAIABNAEEAWAAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgBcAG4AIAAgACAAIAAgACAAIAAgACsAIABpAGcAbgBvAHIAZQBfAGIAbABhAG4AawBzACAAIAAgACAAIAA9ACAAKABvAHAAdABpAG8AbgBhAGwAKQAgAEEAIABUAHIAdQBlAC8ARgBhAGwAcwBlACAAdgBhAGwAdQBlACAAdABvACAAZABlAHQAZQByAG0AaQBuAGUAIAB3AGgAZQB0AGgAZQByACAAbwByACAAbgBvAHQAIABpAG4AYwBsAHUAZABlACAAYgBsAGEAbgBrACAAYwBlAGwAbABzACAAZgByAG8AbQAgAHQAaABlACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAaQBuACAAdABoAGUAIAByAG8AbABsAGkAbgBnACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABoAGUAIABpAG4AcAB1AHQAIABjAGEAbgAgAGIAZQAgAGUAaQB0AGgAZQByACAAVABSAFUARQAvAEYAQQBMAFMARQAgAG8AcgAgADEALwAwAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBmACAAbgBvAHQAIABzAHUAcABwAGwAaQBlAGQALAAgAHcAaQBsAGwAIABkAGUAZgBhAHUAbAB0ACAAdABvACAARgBBAEwAUwBFACAAKAAwACkAXABuACAAIAAgACAAIAAgACAAIAArACAAaQBnAG4AbwByAGUAXwB6AGUAcgBvAHMAIAAgACAAIAAgACAAPQAgACgAbwBwAHQAaQBvAG4AYQBsACkAIABBACAAVAByAHUAZQAvAEYAYQBsAHMAZQAgAHYAYQBsAHUAZQAgAHQAbwAgAGQAZQB0AGUAcgBtAGkAbgBlACAAdwBoAGUAdABoAGUAcgAgAG8AcgAgAG4AbwB0ACAAaQBuAGMAbAB1AGQAZQAgAHoAZQByAG8AIAAoADAAKQAgAHYAYQBsAHUAZQBzACAAZgByAG8AbQAgAHQAaABlACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5ACAAaQBuACAAdABoAGUAIAByAG8AbABsAGkAbgBnACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABoAGUAIABpAG4AcAB1AHQAIABjAGEAbgAgAGIAZQAgAGUAaQB0AGgAZQByACAAVABSAFUARQAvAEYAQQBMAFMARQAgAG8AcgAgADEALwAwAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBmACAAbgBvAHQAIABzAHUAcABwAGwAaQBlAGQALAAgAHcAaQBsAGwAIABkAGUAZgBhAHUAbAB0ACAAdABvACAARgBBAEwAUwBFACAAKAAwACkAXABuACAAIAAgACAAIAAgACAAIAArACAAaQBnAG4AbwByAGUAXwBlAHIAcgBvAHIAcwAgACAAIAAgACAAPQAgACgAbwBwAHQAaQBvAG4AYQBsACkAIABBACAAVAByAHUAZQAvAEYAYQBsAHMAZQAgAHYAYQBsAHUAZQAgAHQAbwAgAGQAZQB0AGUAcgBtAGkAbgBlACAAdwBoAGUAdABoAGUAcgAgAG8AcgAgAG4AbwB0ACAAaQBuAGMAbAB1AGQAZQAgAGUAcgByAG8AcgBzACAAdgBhAGwAdQBlAHMAIAAoAFwAIgAjACAAdgBhAGwAdQBlAHMAXAAiACkAIABmAHIAbwBtACAAdABoAGUAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAIABpAG4AIAB0AGgAZQAgAHIAbwBsAGwAaQBuAGcAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGgAZQAgAGkAbgBwAHUAdAAgAGMAYQBuACAAYgBlACAAZQBpAHQAaABlAHIAIABUAFIAVQBFAC8ARgBBAEwAUwBFACAAbwByACAAMQAvADAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAGYAIABuAG8AdAAgAHMAdQBwAHAAbABpAGUAZAAsACAAdwBpAGwAbAAgAGQAZQBmAGEAdQBsAHQAIAB0AG8AIABGAEEATABTAEUAIAAoADAAKQBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4AbwB0AGUAOgAgACMATgAvAEEAIAB2AGEAbAB1AGUAcwAgAHcAaQBsAGwAIABiAGUAIABlAHgAYwBsAHUAZABlAGQAIABmAHIAbwBtACAAdABoAGUAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AIAByAGUAZwBhAHIAZABsAGUAcwBzACAAbwBmACAAdABoAGkAcwAgAGkAbgBwAHUAdAAgAHAAYQByAGEAbQBlAHQAZQByADsAIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGEAcABwAGwAaQBlAHMAIAB0AG8AIABuAG8AbgAtAE4ALwBBACAAZQByAHIAbwByACAAdgBhAGwAdQBlAHMAXABuACAAIAAgACAAIAAgACAAIAArACAAdgBlAHIAdABpAGMAYQBsAF8AbwB1AHQAcAB1AHQAcwAgACAAPQAgACgAbwBwAHQAaQBvAG4AYQBsACkAIABBACAAVAByAHUAZQAvAEYAYQBsAHMAZQAgAHYAYQBsAHUAZQAgAHcAaABpAGMAaAAgAHcAaQBsAGwAIABmAG8AcgBjAGUAIAB0AGgAZQAgAG8AdQB0AHAAdQB0ACAAbwBmACAAdABoAGUAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AIAB0AG8AIABiAGUAIABlAGkAdABoAGUAcgAgAHYAZQByAHQAaQBjAGEAbAAgACgAVABSAFUARQApACAAbwByACAAaABvAHIAaQB6AG8AbgB0AGEAbAAgACgARgBBAEwAUwBFACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGgAZQAgAGkAbgBwAHUAdAAgAGMAYQBuACAAYgBlACAAZQBpAHQAaABlAHIAIABUAFIAVQBFAC8ARgBBAEwAUwBFACAAbwByACAAMQAvADAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAGYAIABuAG8AdAAgAHMAdQBwAHAAbABpAGUAZAAsACAAdABoAGUAIABvAHUAdABwAHUAdAAgAHcAaQBsAGwAIABiAGUAIABpAG4AIAB0AGgAZQAgAHMAYQBtAGUAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4AIABhAHMAIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGQAYQB0AGEAIABhAHIAcgBhAHkAXABuACAAIAAgACAARQByAHIAbwByACAAYwBvAGQAZQBzADoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACMAQwBBAEwAQwAhACAAIAAgACAAIAAgACAAIAAgACAAPQAgAGEAcgByAGEAeQAgAHAAYQByAGEAbQBlAHQAZQByACAAaQBzACAAaQBuAHYAYQBsAGkAZAAgAC0ALQAgAG4AbwB0ACAAYQAgADEARAAgAGEAcgByAGEAeQAsACAAZQAuAGcALgAgADEAKwAgAHIAbwB3AHMAIABhAG4AZAAgADEAKwAgAGMAbwBsAHUAbQBuAHMAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACMAVgBBAEwAVQBFACEAIAAgACAAIAAgACAAIAAgACAAPQAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAgAHAAYQByAGEAbQBlAHQAZQByACAAaQBzACAAaQBuAHYAYQBsAGkAZAAgAC0ALQAgAG4AbwB0ACAAYQAgAG4AdQBtAGIAZQByACAAYgBlAHQAdwBlAGUAbgAgADEAIABhAG4AZAAgADUAIABvAHIAIABvAG4AZQAgAG8AZgAgAHQAaABlACAAZQB4AHAAZQBjAHQAZQBkAC8AYQBsAGwAbwB3AGUAZAAgAHQAZQB4AHQAIABzAHQAcgBpAG4AZwBzAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAjAFYAQQBMAFUARQAhACAAIAAgACAAIAAgACAAIAAgAD0AIABpAGcAbgBvAHIAZQBfAGIAbABhAG4AawBzACwAIABpAGcAbgBvAHIAZQBfAHoAZQByAG8AcwAsACAAYQBuAGQALwBvAHIAIABpAGcAbgBvAHIAZQBfAGUAcgByAG8AcgBzACAAcABhAHIAYQBtAGUAdABlAHIAcwAgAGEAcgBlACAAaQBuAHYAYQBsAGkAZAAgAC0ALQAgAG4AbwB0ACAAYQAgAG4AdQBtAGIAZQByACAAbwByACAAbABvAGcAaQBjAGEAbAAgACgAQgBvAG8AbABlAGEAbgApACAAdgBhAGwAdQBlAFwAbgAgACAAIAAgAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACAAIAAgACAALQAgAEIAeQAgAGQAZQBmAGEAdQBsAHQAIAB0AGgAZQAgAGYAdQBuAGMAdABpAG8AbgAgAHcAaQBsAGwAIABlAHgAYwBsAHUAZABlACAARQByAHIAbwByACAAdgBhAGwAdQBlAHMAIABmAHIAbwBtACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALAAgAGEAbgBkACAAdABoAGUAIAB1AHMAZQByACAAYwBhAG4AIABjAGgAbwBvAHMAZQAgAHcAaABlAHQAaABlAHIAIAB0AG8AIABhAGwAcwBvACAAZQB4AGMAbAB1AGQAZQAgAGIAbABhAG4AawAgAGMAZQBsAGwAcwAgACgAdwBpAHQAaABpAG4AIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQApACAAbwByACAAegBlAHIAbwAgACgAMAApACAAdgBhAGwAdQBlAHMALgBcAG4AIAAgACAAIAAgACAAIAAgAC0AIABUAGgAZQAgAHIAbwBsAGwAaQBuAGcAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAgACgAaQBuAGMAbAB1AGQAaQBuAGcAIAB0AGgAZQAgAEMATwBVAE4AVAApACAAdwBpAGwAbAAgAG8AbgBsAHkAIABjAG8AbgBzAGkAZABlAHIAIABuAHUAbQBlAHIAaQBjACAAdgBhAGwAdQBlAHMAIABpAG4AIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAsACAAYQBuAGQAIABpAGYAIABiAGwAYQBuAGsAIAB2AGEAbAB1AGUAcwAgAGEAcgBlACAAbgBvAHQAIABlAHgAYwBsAHUAZABlAGQAIAB0AGgAZQB5ACAAdwBpAGwAbAAgAGIAZQAgAHQAcgBlAGEAdABlAGQAIABhAHMAIAB6AGUAcgBvACAAKAAwACkAIAB2AGEAbAB1AGUAcwAuAFwAbgAgACAAIAAgACAAIAAgACAALQAgAEIAeQAgAGQAZQBmAGEAdQBsAHQAIAB0AGgAZQAgAGYAdQBuAGMAdABpAG8AbgAgAHcAaQBsAGwAIABwAHIAbwB2AGkAZABlACAAdABoAGUAIABvAHUAdABwAHUAdAAgAGEAcgByAGEAeQAgACgAcgBvAGwAbABpAG4AZwAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgApACAAaQBuACAAdABoAGUAIABzAGEAbQBlACAAbwByAGkAZQBuAHQAYQB0AGkAbwBuACAAYQBzACAAdABoAGUAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkALAAgAHUAbgBsAGUAcwBzACAAdABoAGUAIAB2AGUAcgB0AGkAYwBhAGwAXwBvAHUAdABwAHUAdAAgAHAAYQByAGEAbQBlAHQAZQByACAAaQBzACAAdQBzAGUAZAAgAHQAbwAgAGYAbwByAGMAZQAgAGEAIABjAGgAbwBzAGUAbgAgAG8AdQB0AHAAdQB0ACAAbwByAGkAZQBuAHQAYQB0AGkAbwBuAC4AXABuACoALwBcAG4AUgBYAEwAXwBSAEMAYQBsAGMAIAA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIAAvAC8AIABQAGEAcgBhAG0AZQB0AGUAcgAgAGQAZQBjAGwAYQByAGEAdABpAG8AbgBzAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAsAFwAbgAgACAAIAAgAFsAaQBnAG4AbwByAGUAXwBiAGwAYQBuAGsAcwBdACwAXABuACAAIAAgACAAWwBpAGcAbgBvAHIAZQBfAHoAZQByAG8AcwBdACwAXABuACAAIAAgACAAWwBpAGcAbgBvAHIAZQBfAGUAcgByAG8AcgBzAF0ALABcAG4AIAAgACAAIABbAHYAZQByAHQAaQBjAGEAbABfAG8AdQB0AHAAdQB0AF0ALABcAG4AIAAgACAAIAAvAC8AIABNAGEAaQBuACAAZgB1AG4AYwB0AGkAbwBuACAAYgBvAGQAeQAvAGMAYQBsAGMAdQBsAGEAdABpAG8AbgBzAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABEAGUAYQBsACAAdwBpAHQAaAAgAHQAaABlACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuACAAcABhAHIAYQBtAGUAdABlAHIAIABpAG4AcAB1AHQAIABhAG4AZAAgAGEAdAB0AGUAbQBwAHQAIAB0AG8AIABtAGEAdABjAGgAIABhAGcAYQBpAG4AcwB0ACAAZQB4AHAAZQBjAHQAZQBkACAAdABlAHgAdAAgAGkAbgBwAHUAdABzACAAaQBmACAAdABoAGUAIABpAG4AcAB1AHQAIABpAHMAIABuAG8AdAAgAGEAIABuAHUAbQBiAGUAcgBcAG4AIAAgACAAIAAgACAAIAAgAF8AbgB1AG0ALAAgAEkARgAoACAASQBTAE4AVQBNAEIARQBSACgAYwBhAGwAYwB1AGwAYQB0AGkAbwBuACkALAAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAsACAASQBGAEUAUgBSAE8AUgAoACAATQBBAFQAQwBIACgATABPAFcARQBSACgAYwBhAGwAYwB1AGwAYQB0AGkAbwBuACkALAAgAHsAXAAiAHMAdQBtAFwAIgAsAFwAIgBjAG8AdQBuAHQAXAAiACwAXAAiAGEAdgBnAFwAIgAsAFwAIgBtAGkAbgBcACIALABcACIAbQBhAHgAXAAiAH0ALAAgADAAKQAsACAAMAApACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEQAZQBhAGwAIAB3AGkAdABoACAAdABoAGUAIABvAHAAdABpAG8AbgBhAGwAIABpAG4AcAB1AHQAIABwAGEAcgBhAG0AZQB0AGUAcgBzACAAYQBuAGQAIABzAGUAdAAgAGQAZQBmAGEAdQBsAHQAIAB2AGEAbAB1AGUAcwAgAGYAbwByACAAYQBuAHkAIABvAG0AaQB0AHQAZQBkACAAcABhAHIAYQBtAGUAdABlAHIAcwBcAG4AIAAgACAAIAAgACAAIAAgAF8AaQBnAEIALAAgAEkARgAoACAASQBTAE8ATQBJAFQAVABFAEQAKABpAGcAbgBvAHIAZQBfAGIAbABhAG4AawBzACkALAAgADAALAAgAGkAZwBuAG8AcgBlAF8AYgBsAGEAbgBrAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXwBpAGcAWgAsACAASQBGACgAIABJAFMATwBNAEkAVABUAEUARAAoAGkAZwBuAG8AcgBlAF8AegBlAHIAbwBzACkALAAgADAALAAgAGkAZwBuAG8AcgBlAF8AegBlAHIAbwBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAF8AaQBnAEUALAAgAEkARgAoACAASQBTAE8ATQBJAFQAVABFAEQAKABpAGcAbgBvAHIAZQBfAGUAcgByAG8AcgBzACkALAAgADAALAAgAGkAZwBuAG8AcgBlAF8AZQByAHIAbwByAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXwB2AE8AdQB0ACwAIABJAEYAKAAgAEkAUwBPAE0ASQBUAFQARQBEACgAdgBlAHIAdABpAGMAYQBsAF8AbwB1AHQAcAB1AHQAKQAsACAALQAxACwAIABJAEYAKAB2AGUAcgB0AGkAYwBhAGwAXwBvAHUAdABwAHUAdAAsACAAMQAsACAAMAApACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAaABlAGMAawAgAGkAbgBwAHUAdAAgAHYAYQBsAGkAZABpAHQAeQBcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgACAALQAtAD4AIABpAG4AdgBhAGwAaQBkACAAYQByAHIAYQB5ACAAaQBuAHAAdQB0ACAAKABuAG8AdAAgAGEAIAAxAEQAIABhAHIAcgBhAHkAKQAgAHcAaQBsAGwAIABnAGkAdgBlACAAYQAgACMAQwBBAEwAQwAhACAAZQByAHIAbwByAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAAIAAtAC0APgAgAGkAbgB2AGEAbABpAGQAIABjAGEAbABjAHUAbABhAHQAaQBvAG4ALAAgAGkAZwBuAG8AcgBlAF8AYgBsAGEAbgBrAHMALAAgAG8AcgAgAGkAZwBuAG8AcgBlAF8AegBlAHIAbwBzACAAcABhAHIAYQBtAGUAdABlAHIAIABpAG4AcAB1AHQAcwAgAHcAaQBsAGwAIABnAGkAdgBlACAAYQAgACMAVgBBAEwAVQBFACEAIABlAHIAcgBvAHIAXABuACAAIAAgACAAIAAgACAAIABfAGkAbgBwAEMAaABrACwAIABJAEYAKAAgAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACAAPgAgADEALAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAgAD4AIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACAAPAAgADEALAAgAEMATwBMAFUATQBOAFMAKABhAHIAcgBhAHkAKQAgADwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKAAgAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAIABOAE8AVAAoAEkAUwBMAE8ARwBJAEMAQQBMACgAXwBpAGcAQgApACkALAAgAE4ATwBUACgASQBTAE4AVQBNAEIARQBSACgAXwBpAGcAQgApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAIABOAE8AVAAoAEkAUwBMAE8ARwBJAEMAQQBMACgAXwBpAGcAWgApACkALAAgAE4ATwBUACgASQBTAE4AVQBNAEIARQBSACgAXwBpAGcAWgApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAIABOAE8AVAAoAEkAUwBMAE8ARwBJAEMAQQBMACgAXwBpAGcARQApACkALAAgAE4ATwBUACgASQBTAE4AVQBNAEIARQBSACgAXwBpAGcARQApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAF8AbgB1AG0AIAA8ACAAMQAsACAAXwBuAHUAbQAgAD4AIAA1ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAzACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARABlAHQAZQByAG0AaQBuAGUAIAB0AGgAZQAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgAgAG8AZgAgAHQAaABlACAAaQBuAHAAdQB0ACAAZABhAHQAYQAgAGEAcgByAGEAeQBcAG4AIAAgACAAIAAgACAAIAAgAF8AdgByAHQALAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAgAD4AIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEYAaQBsAHQAZQByACAAdABoAGUAIABpAG4AcAB1AHQAIABkAGEAdABhACAAYQByAHIAYQB5ACAAZgBvAHIAIABlAHIAcgBvAHIAIAB2AGEAbAB1AGUAcwAsACAAYgBsAGEAbgBrACAAYwBlAGwAbABzACwAIABhAG4AZAAgAHoAZQByAG8AIAAoADAAKQAgAHYAYQBsAHUAZQBzAFwAbgAgACAAIAAgACAAIAAgACAAXwBmAGwAdABFACwAIABJAEYAKABfAGkAZwBFACwAIABJAEYAKAAgAEkAUwBFAFIAUgBPAFIAKABhAHIAcgBhAHkAKQAsACAAXAAiACAAXAAiACwAIABhAHIAcgBhAHkAKQAsACAASQBGAE4AQQAoAGEAcgByAGEAeQAsACAAXAAiACAAXAAiACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXwBmAGwAdABCACwAIABJAEYAKABfAGkAZwBCACwAIABJAEYAKAAgAEkAUwBCAEwAQQBOAEsAKABhAHIAcgBhAHkAKQAsACAAXAAiACAAXAAiACwAIABfAGYAbAB0AEUAKQAsACAAXwBmAGwAdABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAF8AZgBsAHQAWgAsACAASQBGACgAXwBpAGcAWgAsACAASQBGACgAKAAtAC0ATgBPAFQAKABJAFMARQBSAFIATwBSACgAYQByAHIAYQB5ACkAKQAgACoAIAAtAC0ATgBPAFQAKABJAFMAQgBMAEEATgBLACgAYQByAHIAYQB5ACkAKQAgACoAIAAtAC0AKABJAEYARQBSAFIATwBSACgAYQByAHIAYQB5ACwAIABcACIAIABcACIAKQAgAD0AIAAwACkAKQAsACAAXAAiACAAXAAiACwAIABfAGYAbAB0AEIAKQAsACAAXwBmAGwAdABCACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAFMAZQB0ACAAdABoAGUAIABpAG4AaQB0AGkAYQBsACAAdgBhAGwAdQBlACAAZgBvAHIAIAB0AGgAZQAgAHIAbwBsAGwAaQBuAGcAIABNAEkATgAgAGEAbgBkACAATQBBAFgAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwBcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgACAALQAtAD4AIAB1AHMAZQBzACAAdABoAGUAIAB2AGEAbAB1AGUAIABpAG4AIAB0AGgAZQAgAGEAcgByAGEAeQAgAC0ALQAgAGkAZgAgAHQAaABpAHMAIABpAHMAIABuAG8AdAAgAGEAIABuAHUAbQBiAGUAcgAgAHQAaABlAG4AIAB0AGgAZQAgACMATgAvAEEAIABpAHMAIAB1AHMAZQBkACAAaQBuAHMAdABlAGEAZABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgACAALQAtAD4AIABmAG8AcgAgAHQAaABlACAAUwBVAE0ALAAgAEMATwBVAE4AVAAsACAAYQBuAGQAIABBAFYARQBSAEEARwBFACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALAAgAHQAaABlACAAcwB0AGEAcgB0AGkAbgBnACAAdgBhAGwAdQBlACAAaQBzACAAMAAgACgAegBlAHIAbwApAFwAbgAgACAAIAAgACAAIAAgACAAXwBmAHMAdAAsACAASQBOAEQARQBYACgAXwBmAGwAdABaACwAIAAxACwAIAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAF8AaQBuAGkAdAAsACAASQBGACgAKAAtAC0AKABfAGYAcwB0ACAAPAA+ACAAXAAiACAAXAAiACkAIAAqACAALQAtAE4ATwBUACgASQBTAEIATABBAE4ASwAoAF8AZgBzAHQAKQApACAAKgAgAC0ALQAoAEkARgBFAFIAUgBPAFIAKABfAGYAcwB0ACwAIABcACIAIABcACIAKQAgAD0AIAAwACkAKQAsACAAXwBmAHMAdAAsACAATgBBACgAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAvAC8AIABDAGEAbABjAHUAbABhAHQAZQAgAHQAaABlACAAcgBvAGwAbABpAG4AZwAgAFMAVQBNACAAYQBuAGQAIABDAE8AVQBOAFQAIAB2AGEAbAB1AGUAcwAgAHQAbwAgAGIAZQAgAHUAcwBlAGQAIABmAG8AcgAgAHQAaABlACAAUwBVAE0ALAAgAEMATwBVAE4AVAAsACAAbwByACAAQQBWAEUAUgBBAEcARQAgAG8AdQB0AHAAdQB0AHMAXABuACAAIAAgACAAIAAgACAAIABfAHMAdQBtACwAIABJAEYAKAAgAE8AUgAoAF8AbgB1AG0AIAA9ACAAMQAsACAAXwBuAHUAbQAgAD0AIAAzACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBDAEEATgAoADAALAAgAF8AZgBsAHQAWgAsACAATABBAE0AQgBEAEEAKABfAGEAYwBjACwAXwB2AGEAbAAsACAAXwBhAGMAYwAgACsAIABJAEYAKAAgAEkAUwBOAFUATQBCAEUAUgAoAF8AdgBhAGwAKQAsACAAXwB2AGEAbAAsACAAMAApACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXwBjAG4AdAAsACAASQBGACgAIABPAFIAKABfAG4AdQBtACAAPQAgADIALAAgAF8AbgB1AG0AIAA9ACAAMwApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAQwBBAE4AKAAwACwAIABfAGYAbAB0AFoALAAgAEwAQQBNAEIARABBACgAXwBhAGMAYwAsAF8AdgBhAGwALAAgAF8AYQBjAGMAIAArACAASQBGACgAIABJAFMATgBVAE0AQgBFAFIAKABfAHYAYQBsACkALAAgADEALAAgADAAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEMAYQBsAGMAdQBsAGEAdABlACAAdABoAGUAIABjAGgAbwBzAGUAbgAgAG8AdQB0AHAAdQB0ACAAYgBhAHMAZQBkACAAbwBuACAAdABoAGUAIAB1AHMAZQByACAAcwBlAGwAZQBjAHQAZQBkACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuACAAaQBuAHAAdQB0ACAAcABhAHIAYQBtAGUAdABlAHIAXABuACAAIAAgACAAIAAgACAAIABfAG8AdQB0ACwAIABDAEgATwBPAFMARQAoAF8AbgB1AG0ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXwBzAHUAbQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAGMAbgB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAF8AYwBuAHQAIAA8AD4AIAAwACwAIABfAHMAdQBtACAALwAgAF8AYwBuAHQALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEMAQQBOACgAXwBpAG4AaQB0ACwAIABfAGYAbAB0AFoALAAgAEwAQQBNAEIARABBACgAXwBhAGMAYwAsAF8AdgBhAGwALAAgAEkARgBTACgAIABBAE4ARAAoACAASQBTAE4AQQAoAF8AYQBjAGMAKQAsACAASQBTAE4AVQBNAEIARQBSACgAXwB2AGEAbAApACkALAAgAF8AdgBhAGwALAAgAEkAUwBOAFUATQBCAEUAUgAoAF8AdgBhAGwAKQAsACAATQBJAE4AKABfAGEAYwBjACwAIABfAHYAYQBsACkALAAgAFQAUgBVAEUALAAgAF8AYQBjAGMAKQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBDAEEATgAoAF8AaQBuAGkAdAAsACAAXwBmAGwAdABaACwAIABMAEEATQBCAEQAQQAoAF8AYQBjAGMALABfAHYAYQBsACwAIABJAEYAUwAoACAAQQBOAEQAKAAgAEkAUwBOAEEAKABfAGEAYwBjACkALAAgAEkAUwBOAFUATQBCAEUAUgAoAF8AdgBhAGwAKQApACwAIABfAHYAYQBsACwAIABJAFMATgBVAE0AQgBFAFIAKABfAHYAYQBsACkALAAgAE0AQQBYACgAXwBhAGMAYwAsACAAXwB2AGEAbAApACwAIABUAFIAVQBFACwAIABfAGEAYwBjACkAKQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAALwAvACAARABlAHQAZQByAG0AaQBuAGUAIAB3AGgAZQB0AGgAZQByACAAdABvACAAZgBvAHIAYwBlACAAYQAgAHAAYQByAHQAaQBjAHUAbABhAHIAIABvAHUAdABwAHUAdAAgAG8AcgBpAGUAbgB0AGEAdABpAG8AbgAgAGEAbgBkACAAdAByAGEAbgBzAHAAbwBzAGUAIAB0AGgAZQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABvAHUAdABwAHUAdAAgAGEAcwAgAHIAZQBxAHUAaQByAGUAZABcAG4AIAAgACAAIAAgACAAIAAgAF8AcgB0AG4ALAAgAEkARgBTACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAF8AdgBPAHUAdAAgADwAIAAwACwAIABfAG8AdQB0ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAXwB2AE8AdQB0ACwAIABOAE8AVAAoAF8AdgByAHQAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQQBOAEQAKABOAE8AVAAoAF8AdgBPAHUAdAApACwAIABfAHYAcgB0ACkAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABSAEEATgBTAFAATwBTAEUAKABfAG8AdQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABSAFUARQAsACAAXwBvAHUAdABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8ALwAgAEkAZgAgAHQAaABlACAAaQBuAHAAdQB0ACAAYwBoAGUAYwBrAHMAIAAoAF8AaQBuAHAAQwBoAGsAKQAgAGgAYQB2AGUAIABmAGwAYQBnAGcAZQBkACAAdABoAGUAbgAgAHIAZQB0AHUAcgBuACAAdABoAGUAIAByAGUAcQB1AGkAcgBlAGQAIABFAHgAYwBlAGwAIABlAHIAcgBvAHIAIABjAG8AZABlACwAIABvAHQAaABlAHIAdwBpAHMAZQAgAHIAZQB0AHUAcgBuACAAdABoAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAcgBlAHMAdQBsAHQAIAAoAF8AcgB0AG4AKQBcAG4AIAAgACAAIAAgACAAIAAgAEMASABPAE8AUwBFACgAXwBpAG4AcABDAGgAawAsACAAXwByAHQAbgAsACAATABBAE0AQgBEAEEAKAAwACkALAAgACMAVgBBAEwAVQBFACEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAUgBYAEwAXwBSAEMAYQBsAGMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAowAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
